--- a/data/KEC_Table.xlsx
+++ b/data/KEC_Table.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\업무자료실(윤태석)\00 내역서프로그램\web_kec_cable_calculator\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\모든현장\업무자료실(윤태석)\00 내역서프로그램\web_kec_cable_calculator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B82F37F-2CF9-4E3B-BB73-6B16B3A45D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="817" activeTab="3" xr2:uid="{AC531F24-1C8D-4371-836F-38D87657C46C}"/>
+    <workbookView xWindow="-118" yWindow="-118" windowWidth="29036" windowHeight="15840" tabRatio="817" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="cable_spec" sheetId="256" r:id="rId1"/>
@@ -122,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="498">
   <si>
     <t>-</t>
   </si>
@@ -2097,14 +2096,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="0.00_);\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0.0;[Red]0.0"/>
     <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="바탕체"/>
@@ -2485,7 +2484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2795,6 +2794,9 @@
     <xf numFmtId="179" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2883,72 +2885,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>459115</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>82098</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CE6D1CA-3659-4481-9426-5F3CB2A50AE3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3848100" y="152400"/>
-          <a:ext cx="1830715" cy="1148898"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3306,20 +3242,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A58941-7CC6-4C1E-BF8A-F43899C3F3DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet31">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:D413"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.8" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="7.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.125" style="65" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="65" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="9" t="s">
         <v>53</v>
       </c>
@@ -3331,7 +3267,7 @@
       </c>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="11" t="s">
         <v>99</v>
       </c>
@@ -3343,7 +3279,7 @@
       </c>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="11" t="s">
         <v>100</v>
       </c>
@@ -3355,7 +3291,7 @@
       </c>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="11" t="s">
         <v>105</v>
       </c>
@@ -3367,7 +3303,7 @@
       </c>
       <c r="D4" s="6"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="11" t="s">
         <v>110</v>
       </c>
@@ -3379,7 +3315,7 @@
       </c>
       <c r="D5" s="6"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="11" t="s">
         <v>153</v>
       </c>
@@ -3391,7 +3327,7 @@
       </c>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="11" t="s">
         <v>155</v>
       </c>
@@ -3403,7 +3339,7 @@
       </c>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="11" t="s">
         <v>161</v>
       </c>
@@ -3415,7 +3351,7 @@
       </c>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="11" t="s">
         <v>167</v>
       </c>
@@ -3427,7 +3363,7 @@
       </c>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="11" t="s">
         <v>211</v>
       </c>
@@ -3439,7 +3375,7 @@
       </c>
       <c r="D10" s="6"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="11" t="s">
         <v>213</v>
       </c>
@@ -3451,7 +3387,7 @@
       </c>
       <c r="D11" s="6"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" s="11" t="s">
         <v>219</v>
       </c>
@@ -3463,7 +3399,7 @@
       </c>
       <c r="D12" s="6"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" s="11" t="s">
         <v>225</v>
       </c>
@@ -3475,7 +3411,7 @@
       </c>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="11" t="s">
         <v>269</v>
       </c>
@@ -3487,7 +3423,7 @@
       </c>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="11" t="s">
         <v>271</v>
       </c>
@@ -3499,7 +3435,7 @@
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" s="11" t="s">
         <v>276</v>
       </c>
@@ -3511,7 +3447,7 @@
       </c>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="11" t="s">
         <v>281</v>
       </c>
@@ -3523,7 +3459,7 @@
       </c>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="11" t="s">
         <v>315</v>
       </c>
@@ -3535,7 +3471,7 @@
       </c>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="11" t="s">
         <v>317</v>
       </c>
@@ -3547,7 +3483,7 @@
       </c>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="11" t="s">
         <v>322</v>
       </c>
@@ -3559,7 +3495,7 @@
       </c>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="11" t="s">
         <v>327</v>
       </c>
@@ -3571,7 +3507,7 @@
       </c>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="11" t="s">
         <v>361</v>
       </c>
@@ -3583,7 +3519,7 @@
       </c>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="11" t="s">
         <v>363</v>
       </c>
@@ -3595,7 +3531,7 @@
       </c>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="11" t="s">
         <v>365</v>
       </c>
@@ -3607,7 +3543,7 @@
       </c>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="11" t="s">
         <v>367</v>
       </c>
@@ -3619,7 +3555,7 @@
       </c>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="11" t="s">
         <v>371</v>
       </c>
@@ -3631,7 +3567,7 @@
       </c>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="11" t="s">
         <v>373</v>
       </c>
@@ -3643,7 +3579,7 @@
       </c>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="11" t="s">
         <v>375</v>
       </c>
@@ -3655,7 +3591,7 @@
       </c>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="11" t="s">
         <v>377</v>
       </c>
@@ -3667,7 +3603,7 @@
       </c>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="11" t="s">
         <v>381</v>
       </c>
@@ -3679,7 +3615,7 @@
       </c>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="11" t="s">
         <v>383</v>
       </c>
@@ -3691,7 +3627,7 @@
       </c>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="11" t="s">
         <v>385</v>
       </c>
@@ -3703,7 +3639,7 @@
       </c>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="11" t="s">
         <v>387</v>
       </c>
@@ -3715,7 +3651,7 @@
       </c>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="11" t="s">
         <v>391</v>
       </c>
@@ -3727,7 +3663,7 @@
       </c>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="11" t="s">
         <v>393</v>
       </c>
@@ -3739,7 +3675,7 @@
       </c>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="11" t="s">
         <v>395</v>
       </c>
@@ -3751,7 +3687,7 @@
       </c>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="11" t="s">
         <v>397</v>
       </c>
@@ -3763,7 +3699,7 @@
       </c>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="11" t="s">
         <v>401</v>
       </c>
@@ -3775,7 +3711,7 @@
       </c>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="11" t="s">
         <v>403</v>
       </c>
@@ -3787,7 +3723,7 @@
       </c>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="11" t="s">
         <v>405</v>
       </c>
@@ -3799,7 +3735,7 @@
       </c>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="11" t="s">
         <v>407</v>
       </c>
@@ -3811,7 +3747,7 @@
       </c>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="11" t="s">
         <v>411</v>
       </c>
@@ -3823,7 +3759,7 @@
       </c>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="11" t="s">
         <v>413</v>
       </c>
@@ -3835,7 +3771,7 @@
       </c>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="11" t="s">
         <v>415</v>
       </c>
@@ -3847,7 +3783,7 @@
       </c>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="11" t="s">
         <v>417</v>
       </c>
@@ -3859,7 +3795,7 @@
       </c>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="11" t="s">
         <v>421</v>
       </c>
@@ -3871,7 +3807,7 @@
       </c>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="11" t="s">
         <v>423</v>
       </c>
@@ -3883,7 +3819,7 @@
       </c>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="11" t="s">
         <v>425</v>
       </c>
@@ -3895,7 +3831,7 @@
       </c>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" s="11" t="s">
         <v>427</v>
       </c>
@@ -3907,7 +3843,7 @@
       </c>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="11" t="s">
         <v>431</v>
       </c>
@@ -3919,7 +3855,7 @@
       </c>
       <c r="D50" s="6"/>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" s="11" t="s">
         <v>433</v>
       </c>
@@ -3931,7 +3867,7 @@
       </c>
       <c r="D51" s="6"/>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="11" t="s">
         <v>435</v>
       </c>
@@ -3943,7 +3879,7 @@
       </c>
       <c r="D52" s="6"/>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="11" t="s">
         <v>437</v>
       </c>
@@ -3955,7 +3891,7 @@
       </c>
       <c r="D53" s="6"/>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" s="11" t="s">
         <v>441</v>
       </c>
@@ -3967,7 +3903,7 @@
       </c>
       <c r="D54" s="6"/>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" s="11" t="s">
         <v>443</v>
       </c>
@@ -3979,7 +3915,7 @@
       </c>
       <c r="D55" s="6"/>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" s="11" t="s">
         <v>445</v>
       </c>
@@ -3991,7 +3927,7 @@
       </c>
       <c r="D56" s="6"/>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" s="11" t="s">
         <v>447</v>
       </c>
@@ -4003,7 +3939,7 @@
       </c>
       <c r="D57" s="6"/>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" s="11" t="s">
         <v>451</v>
       </c>
@@ -4015,7 +3951,7 @@
       </c>
       <c r="D58" s="6"/>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" s="11" t="s">
         <v>453</v>
       </c>
@@ -4027,7 +3963,7 @@
       </c>
       <c r="D59" s="6"/>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" s="11" t="s">
         <v>455</v>
       </c>
@@ -4039,7 +3975,7 @@
       </c>
       <c r="D60" s="6"/>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61" s="11" t="s">
         <v>457</v>
       </c>
@@ -4051,7 +3987,7 @@
       </c>
       <c r="D61" s="6"/>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62" s="11" t="s">
         <v>461</v>
       </c>
@@ -4063,7 +3999,7 @@
       </c>
       <c r="D62" s="6"/>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A63" s="11" t="s">
         <v>463</v>
       </c>
@@ -4075,7 +4011,7 @@
       </c>
       <c r="D63" s="6"/>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A64" s="11" t="s">
         <v>465</v>
       </c>
@@ -4087,7 +4023,7 @@
       </c>
       <c r="D64" s="6"/>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="11" t="s">
         <v>467</v>
       </c>
@@ -4099,7 +4035,7 @@
       </c>
       <c r="D65" s="6"/>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="11" t="s">
         <v>471</v>
       </c>
@@ -4111,7 +4047,7 @@
       </c>
       <c r="D66" s="6"/>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="11" t="s">
         <v>473</v>
       </c>
@@ -4119,7 +4055,7 @@
       <c r="C67" s="64"/>
       <c r="D67" s="6"/>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="11" t="s">
         <v>475</v>
       </c>
@@ -4127,7 +4063,7 @@
       <c r="C68" s="64"/>
       <c r="D68" s="6"/>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="11" t="s">
         <v>476</v>
       </c>
@@ -4135,7 +4071,7 @@
       <c r="C69" s="64"/>
       <c r="D69" s="6"/>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="11" t="s">
         <v>479</v>
       </c>
@@ -4147,7 +4083,7 @@
       </c>
       <c r="D70" s="6"/>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="11" t="s">
         <v>481</v>
       </c>
@@ -4155,7 +4091,7 @@
       <c r="C71" s="64"/>
       <c r="D71" s="6"/>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" s="11" t="s">
         <v>483</v>
       </c>
@@ -4163,7 +4099,7 @@
       <c r="C72" s="64"/>
       <c r="D72" s="6"/>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="11" t="s">
         <v>484</v>
       </c>
@@ -4171,7 +4107,7 @@
       <c r="C73" s="64"/>
       <c r="D73" s="6"/>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="11" t="s">
         <v>486</v>
       </c>
@@ -4183,7 +4119,7 @@
       </c>
       <c r="D74" s="6"/>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="11" t="s">
         <v>488</v>
       </c>
@@ -4191,7 +4127,7 @@
       <c r="C75" s="64"/>
       <c r="D75" s="6"/>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="11" t="s">
         <v>490</v>
       </c>
@@ -4199,7 +4135,7 @@
       <c r="C76" s="64"/>
       <c r="D76" s="6"/>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="11" t="s">
         <v>491</v>
       </c>
@@ -4207,7 +4143,7 @@
       <c r="C77" s="64"/>
       <c r="D77" s="6"/>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="11" t="s">
         <v>101</v>
       </c>
@@ -4219,7 +4155,7 @@
       </c>
       <c r="D78" s="6"/>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="11" t="s">
         <v>106</v>
       </c>
@@ -4231,7 +4167,7 @@
       </c>
       <c r="D79" s="6"/>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="11" t="s">
         <v>111</v>
       </c>
@@ -4243,7 +4179,7 @@
       </c>
       <c r="D80" s="6"/>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="11" t="s">
         <v>115</v>
       </c>
@@ -4255,7 +4191,7 @@
       </c>
       <c r="D81" s="6"/>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="11" t="s">
         <v>119</v>
       </c>
@@ -4267,7 +4203,7 @@
       </c>
       <c r="D82" s="6"/>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="11" t="s">
         <v>123</v>
       </c>
@@ -4279,7 +4215,7 @@
       </c>
       <c r="D83" s="6"/>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="11" t="s">
         <v>127</v>
       </c>
@@ -4291,7 +4227,7 @@
       </c>
       <c r="D84" s="6"/>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="11" t="s">
         <v>131</v>
       </c>
@@ -4303,7 +4239,7 @@
       </c>
       <c r="D85" s="6"/>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="11" t="s">
         <v>135</v>
       </c>
@@ -4315,7 +4251,7 @@
       </c>
       <c r="D86" s="6"/>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="11" t="s">
         <v>139</v>
       </c>
@@ -4327,7 +4263,7 @@
       </c>
       <c r="D87" s="6"/>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="11" t="s">
         <v>143</v>
       </c>
@@ -4339,7 +4275,7 @@
       </c>
       <c r="D88" s="6"/>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="11" t="s">
         <v>147</v>
       </c>
@@ -4351,7 +4287,7 @@
       </c>
       <c r="D89" s="6"/>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="11" t="s">
         <v>156</v>
       </c>
@@ -4363,7 +4299,7 @@
       </c>
       <c r="D90" s="6"/>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="11" t="s">
         <v>162</v>
       </c>
@@ -4375,7 +4311,7 @@
       </c>
       <c r="D91" s="6"/>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="11" t="s">
         <v>168</v>
       </c>
@@ -4387,7 +4323,7 @@
       </c>
       <c r="D92" s="6"/>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="11" t="s">
         <v>173</v>
       </c>
@@ -4399,7 +4335,7 @@
       </c>
       <c r="D93" s="6"/>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="11" t="s">
         <v>177</v>
       </c>
@@ -4411,7 +4347,7 @@
       </c>
       <c r="D94" s="6"/>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="11" t="s">
         <v>181</v>
       </c>
@@ -4423,7 +4359,7 @@
       </c>
       <c r="D95" s="6"/>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="11" t="s">
         <v>185</v>
       </c>
@@ -4435,7 +4371,7 @@
       </c>
       <c r="D96" s="6"/>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="11" t="s">
         <v>189</v>
       </c>
@@ -4447,7 +4383,7 @@
       </c>
       <c r="D97" s="6"/>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="11" t="s">
         <v>193</v>
       </c>
@@ -4459,7 +4395,7 @@
       </c>
       <c r="D98" s="6"/>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="11" t="s">
         <v>197</v>
       </c>
@@ -4471,7 +4407,7 @@
       </c>
       <c r="D99" s="6"/>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="11" t="s">
         <v>201</v>
       </c>
@@ -4483,7 +4419,7 @@
       </c>
       <c r="D100" s="6"/>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="11" t="s">
         <v>205</v>
       </c>
@@ -4495,7 +4431,7 @@
       </c>
       <c r="D101" s="6"/>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="11" t="s">
         <v>214</v>
       </c>
@@ -4507,7 +4443,7 @@
       </c>
       <c r="D102" s="6"/>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="11" t="s">
         <v>220</v>
       </c>
@@ -4519,7 +4455,7 @@
       </c>
       <c r="D103" s="6"/>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="11" t="s">
         <v>226</v>
       </c>
@@ -4531,7 +4467,7 @@
       </c>
       <c r="D104" s="6"/>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="11" t="s">
         <v>231</v>
       </c>
@@ -4543,7 +4479,7 @@
       </c>
       <c r="D105" s="6"/>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="11" t="s">
         <v>235</v>
       </c>
@@ -4555,7 +4491,7 @@
       </c>
       <c r="D106" s="6"/>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" s="11" t="s">
         <v>239</v>
       </c>
@@ -4567,7 +4503,7 @@
       </c>
       <c r="D107" s="6"/>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A108" s="11" t="s">
         <v>243</v>
       </c>
@@ -4579,7 +4515,7 @@
       </c>
       <c r="D108" s="6"/>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A109" s="11" t="s">
         <v>247</v>
       </c>
@@ -4591,7 +4527,7 @@
       </c>
       <c r="D109" s="6"/>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A110" s="11" t="s">
         <v>251</v>
       </c>
@@ -4603,7 +4539,7 @@
       </c>
       <c r="D110" s="6"/>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A111" s="11" t="s">
         <v>255</v>
       </c>
@@ -4615,7 +4551,7 @@
       </c>
       <c r="D111" s="6"/>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A112" s="11" t="s">
         <v>259</v>
       </c>
@@ -4627,7 +4563,7 @@
       </c>
       <c r="D112" s="6"/>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A113" s="11" t="s">
         <v>263</v>
       </c>
@@ -4639,7 +4575,7 @@
       </c>
       <c r="D113" s="6"/>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A114" s="11" t="s">
         <v>272</v>
       </c>
@@ -4651,7 +4587,7 @@
       </c>
       <c r="D114" s="6"/>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A115" s="11" t="s">
         <v>277</v>
       </c>
@@ -4663,7 +4599,7 @@
       </c>
       <c r="D115" s="6"/>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A116" s="11" t="s">
         <v>282</v>
       </c>
@@ -4675,7 +4611,7 @@
       </c>
       <c r="D116" s="6"/>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A117" s="11" t="s">
         <v>286</v>
       </c>
@@ -4687,7 +4623,7 @@
       </c>
       <c r="D117" s="6"/>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A118" s="11" t="s">
         <v>289</v>
       </c>
@@ -4699,7 +4635,7 @@
       </c>
       <c r="D118" s="6"/>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A119" s="11" t="s">
         <v>292</v>
       </c>
@@ -4711,7 +4647,7 @@
       </c>
       <c r="D119" s="6"/>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A120" s="11" t="s">
         <v>295</v>
       </c>
@@ -4723,7 +4659,7 @@
       </c>
       <c r="D120" s="6"/>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A121" s="11" t="s">
         <v>298</v>
       </c>
@@ -4735,7 +4671,7 @@
       </c>
       <c r="D121" s="6"/>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A122" s="11" t="s">
         <v>301</v>
       </c>
@@ -4747,7 +4683,7 @@
       </c>
       <c r="D122" s="6"/>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A123" s="11" t="s">
         <v>304</v>
       </c>
@@ -4759,7 +4695,7 @@
       </c>
       <c r="D123" s="6"/>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A124" s="11" t="s">
         <v>307</v>
       </c>
@@ -4771,7 +4707,7 @@
       </c>
       <c r="D124" s="6"/>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A125" s="11" t="s">
         <v>310</v>
       </c>
@@ -4779,7 +4715,7 @@
       <c r="C125" s="64"/>
       <c r="D125" s="6"/>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A126" s="11" t="s">
         <v>318</v>
       </c>
@@ -4791,7 +4727,7 @@
       </c>
       <c r="D126" s="6"/>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A127" s="11" t="s">
         <v>323</v>
       </c>
@@ -4803,7 +4739,7 @@
       </c>
       <c r="D127" s="6"/>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A128" s="11" t="s">
         <v>328</v>
       </c>
@@ -4815,7 +4751,7 @@
       </c>
       <c r="D128" s="6"/>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A129" s="11" t="s">
         <v>332</v>
       </c>
@@ -4827,7 +4763,7 @@
       </c>
       <c r="D129" s="6"/>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A130" s="11" t="s">
         <v>335</v>
       </c>
@@ -4839,7 +4775,7 @@
       </c>
       <c r="D130" s="6"/>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A131" s="11" t="s">
         <v>338</v>
       </c>
@@ -4851,7 +4787,7 @@
       </c>
       <c r="D131" s="6"/>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A132" s="11" t="s">
         <v>341</v>
       </c>
@@ -4863,7 +4799,7 @@
       </c>
       <c r="D132" s="6"/>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A133" s="11" t="s">
         <v>344</v>
       </c>
@@ -4875,7 +4811,7 @@
       </c>
       <c r="D133" s="6"/>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A134" s="11" t="s">
         <v>347</v>
       </c>
@@ -4887,7 +4823,7 @@
       </c>
       <c r="D134" s="6"/>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A135" s="11" t="s">
         <v>350</v>
       </c>
@@ -4895,7 +4831,7 @@
       <c r="C135" s="64"/>
       <c r="D135" s="6"/>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A136" s="11" t="s">
         <v>353</v>
       </c>
@@ -4903,7 +4839,7 @@
       <c r="C136" s="64"/>
       <c r="D136" s="6"/>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A137" s="11" t="s">
         <v>356</v>
       </c>
@@ -4911,7 +4847,7 @@
       <c r="C137" s="64"/>
       <c r="D137" s="6"/>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A138" s="11" t="s">
         <v>102</v>
       </c>
@@ -4923,7 +4859,7 @@
       </c>
       <c r="D138" s="6"/>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A139" s="11" t="s">
         <v>107</v>
       </c>
@@ -4935,7 +4871,7 @@
       </c>
       <c r="D139" s="6"/>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A140" s="11" t="s">
         <v>112</v>
       </c>
@@ -4947,7 +4883,7 @@
       </c>
       <c r="D140" s="6"/>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A141" s="11" t="s">
         <v>116</v>
       </c>
@@ -4959,7 +4895,7 @@
       </c>
       <c r="D141" s="6"/>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A142" s="11" t="s">
         <v>120</v>
       </c>
@@ -4971,7 +4907,7 @@
       </c>
       <c r="D142" s="6"/>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A143" s="11" t="s">
         <v>124</v>
       </c>
@@ -4983,7 +4919,7 @@
       </c>
       <c r="D143" s="6"/>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A144" s="11" t="s">
         <v>128</v>
       </c>
@@ -4995,7 +4931,7 @@
       </c>
       <c r="D144" s="6"/>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A145" s="11" t="s">
         <v>132</v>
       </c>
@@ -5007,7 +4943,7 @@
       </c>
       <c r="D145" s="6"/>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A146" s="11" t="s">
         <v>136</v>
       </c>
@@ -5019,7 +4955,7 @@
       </c>
       <c r="D146" s="6"/>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A147" s="11" t="s">
         <v>140</v>
       </c>
@@ -5031,7 +4967,7 @@
       </c>
       <c r="D147" s="6"/>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A148" s="11" t="s">
         <v>144</v>
       </c>
@@ -5043,7 +4979,7 @@
       </c>
       <c r="D148" s="6"/>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A149" s="11" t="s">
         <v>148</v>
       </c>
@@ -5055,7 +4991,7 @@
       </c>
       <c r="D149" s="6"/>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A150" s="11" t="s">
         <v>157</v>
       </c>
@@ -5067,7 +5003,7 @@
       </c>
       <c r="D150" s="6"/>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A151" s="11" t="s">
         <v>163</v>
       </c>
@@ -5079,7 +5015,7 @@
       </c>
       <c r="D151" s="6"/>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A152" s="11" t="s">
         <v>169</v>
       </c>
@@ -5091,7 +5027,7 @@
       </c>
       <c r="D152" s="6"/>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A153" s="11" t="s">
         <v>174</v>
       </c>
@@ -5103,7 +5039,7 @@
       </c>
       <c r="D153" s="6"/>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A154" s="11" t="s">
         <v>178</v>
       </c>
@@ -5115,7 +5051,7 @@
       </c>
       <c r="D154" s="6"/>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A155" s="11" t="s">
         <v>182</v>
       </c>
@@ -5127,7 +5063,7 @@
       </c>
       <c r="D155" s="6"/>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A156" s="11" t="s">
         <v>186</v>
       </c>
@@ -5139,7 +5075,7 @@
       </c>
       <c r="D156" s="6"/>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A157" s="11" t="s">
         <v>190</v>
       </c>
@@ -5151,7 +5087,7 @@
       </c>
       <c r="D157" s="6"/>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A158" s="11" t="s">
         <v>194</v>
       </c>
@@ -5163,7 +5099,7 @@
       </c>
       <c r="D158" s="6"/>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A159" s="11" t="s">
         <v>198</v>
       </c>
@@ -5175,7 +5111,7 @@
       </c>
       <c r="D159" s="6"/>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A160" s="11" t="s">
         <v>202</v>
       </c>
@@ -5187,7 +5123,7 @@
       </c>
       <c r="D160" s="6"/>
     </row>
-    <row r="161" spans="1:4">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A161" s="11" t="s">
         <v>206</v>
       </c>
@@ -5199,7 +5135,7 @@
       </c>
       <c r="D161" s="6"/>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A162" s="11" t="s">
         <v>215</v>
       </c>
@@ -5211,7 +5147,7 @@
       </c>
       <c r="D162" s="6"/>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A163" s="11" t="s">
         <v>221</v>
       </c>
@@ -5223,7 +5159,7 @@
       </c>
       <c r="D163" s="6"/>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A164" s="11" t="s">
         <v>227</v>
       </c>
@@ -5235,7 +5171,7 @@
       </c>
       <c r="D164" s="6"/>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A165" s="11" t="s">
         <v>232</v>
       </c>
@@ -5247,7 +5183,7 @@
       </c>
       <c r="D165" s="6"/>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A166" s="11" t="s">
         <v>236</v>
       </c>
@@ -5259,7 +5195,7 @@
       </c>
       <c r="D166" s="6"/>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A167" s="11" t="s">
         <v>240</v>
       </c>
@@ -5271,7 +5207,7 @@
       </c>
       <c r="D167" s="6"/>
     </row>
-    <row r="168" spans="1:4">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A168" s="11" t="s">
         <v>244</v>
       </c>
@@ -5283,7 +5219,7 @@
       </c>
       <c r="D168" s="6"/>
     </row>
-    <row r="169" spans="1:4">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A169" s="11" t="s">
         <v>248</v>
       </c>
@@ -5295,7 +5231,7 @@
       </c>
       <c r="D169" s="6"/>
     </row>
-    <row r="170" spans="1:4">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A170" s="11" t="s">
         <v>252</v>
       </c>
@@ -5307,7 +5243,7 @@
       </c>
       <c r="D170" s="6"/>
     </row>
-    <row r="171" spans="1:4">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A171" s="11" t="s">
         <v>256</v>
       </c>
@@ -5319,7 +5255,7 @@
       </c>
       <c r="D171" s="6"/>
     </row>
-    <row r="172" spans="1:4">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A172" s="11" t="s">
         <v>260</v>
       </c>
@@ -5331,7 +5267,7 @@
       </c>
       <c r="D172" s="6"/>
     </row>
-    <row r="173" spans="1:4">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A173" s="11" t="s">
         <v>264</v>
       </c>
@@ -5343,7 +5279,7 @@
       </c>
       <c r="D173" s="6"/>
     </row>
-    <row r="174" spans="1:4">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A174" s="11" t="s">
         <v>273</v>
       </c>
@@ -5355,7 +5291,7 @@
       </c>
       <c r="D174" s="6"/>
     </row>
-    <row r="175" spans="1:4">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A175" s="11" t="s">
         <v>278</v>
       </c>
@@ -5367,7 +5303,7 @@
       </c>
       <c r="D175" s="6"/>
     </row>
-    <row r="176" spans="1:4">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A176" s="11" t="s">
         <v>283</v>
       </c>
@@ -5379,7 +5315,7 @@
       </c>
       <c r="D176" s="6"/>
     </row>
-    <row r="177" spans="1:4">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A177" s="11" t="s">
         <v>287</v>
       </c>
@@ -5391,7 +5327,7 @@
       </c>
       <c r="D177" s="6"/>
     </row>
-    <row r="178" spans="1:4">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A178" s="11" t="s">
         <v>290</v>
       </c>
@@ -5403,7 +5339,7 @@
       </c>
       <c r="D178" s="6"/>
     </row>
-    <row r="179" spans="1:4">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A179" s="11" t="s">
         <v>293</v>
       </c>
@@ -5415,7 +5351,7 @@
       </c>
       <c r="D179" s="6"/>
     </row>
-    <row r="180" spans="1:4">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A180" s="11" t="s">
         <v>296</v>
       </c>
@@ -5427,7 +5363,7 @@
       </c>
       <c r="D180" s="6"/>
     </row>
-    <row r="181" spans="1:4">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A181" s="11" t="s">
         <v>299</v>
       </c>
@@ -5439,7 +5375,7 @@
       </c>
       <c r="D181" s="6"/>
     </row>
-    <row r="182" spans="1:4">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A182" s="11" t="s">
         <v>302</v>
       </c>
@@ -5451,7 +5387,7 @@
       </c>
       <c r="D182" s="6"/>
     </row>
-    <row r="183" spans="1:4">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A183" s="11" t="s">
         <v>305</v>
       </c>
@@ -5463,7 +5399,7 @@
       </c>
       <c r="D183" s="6"/>
     </row>
-    <row r="184" spans="1:4">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A184" s="11" t="s">
         <v>308</v>
       </c>
@@ -5475,7 +5411,7 @@
       </c>
       <c r="D184" s="6"/>
     </row>
-    <row r="185" spans="1:4">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A185" s="11" t="s">
         <v>311</v>
       </c>
@@ -5483,7 +5419,7 @@
       <c r="C185" s="64"/>
       <c r="D185" s="6"/>
     </row>
-    <row r="186" spans="1:4">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A186" s="11" t="s">
         <v>319</v>
       </c>
@@ -5495,7 +5431,7 @@
       </c>
       <c r="D186" s="6"/>
     </row>
-    <row r="187" spans="1:4">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A187" s="11" t="s">
         <v>324</v>
       </c>
@@ -5507,7 +5443,7 @@
       </c>
       <c r="D187" s="6"/>
     </row>
-    <row r="188" spans="1:4">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A188" s="11" t="s">
         <v>329</v>
       </c>
@@ -5519,7 +5455,7 @@
       </c>
       <c r="D188" s="6"/>
     </row>
-    <row r="189" spans="1:4">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A189" s="11" t="s">
         <v>333</v>
       </c>
@@ -5531,7 +5467,7 @@
       </c>
       <c r="D189" s="6"/>
     </row>
-    <row r="190" spans="1:4">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A190" s="11" t="s">
         <v>336</v>
       </c>
@@ -5543,7 +5479,7 @@
       </c>
       <c r="D190" s="6"/>
     </row>
-    <row r="191" spans="1:4">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A191" s="11" t="s">
         <v>339</v>
       </c>
@@ -5555,7 +5491,7 @@
       </c>
       <c r="D191" s="6"/>
     </row>
-    <row r="192" spans="1:4">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A192" s="11" t="s">
         <v>342</v>
       </c>
@@ -5567,7 +5503,7 @@
       </c>
       <c r="D192" s="6"/>
     </row>
-    <row r="193" spans="1:4">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A193" s="11" t="s">
         <v>345</v>
       </c>
@@ -5579,7 +5515,7 @@
       </c>
       <c r="D193" s="6"/>
     </row>
-    <row r="194" spans="1:4">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A194" s="11" t="s">
         <v>348</v>
       </c>
@@ -5591,7 +5527,7 @@
       </c>
       <c r="D194" s="6"/>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A195" s="11" t="s">
         <v>351</v>
       </c>
@@ -5599,7 +5535,7 @@
       <c r="C195" s="64"/>
       <c r="D195" s="6"/>
     </row>
-    <row r="196" spans="1:4">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A196" s="11" t="s">
         <v>354</v>
       </c>
@@ -5607,7 +5543,7 @@
       <c r="C196" s="64"/>
       <c r="D196" s="6"/>
     </row>
-    <row r="197" spans="1:4">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A197" s="11" t="s">
         <v>357</v>
       </c>
@@ -5615,7 +5551,7 @@
       <c r="C197" s="64"/>
       <c r="D197" s="6"/>
     </row>
-    <row r="198" spans="1:4">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A198" s="11" t="s">
         <v>103</v>
       </c>
@@ -5627,7 +5563,7 @@
       </c>
       <c r="D198" s="6"/>
     </row>
-    <row r="199" spans="1:4">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A199" s="11" t="s">
         <v>108</v>
       </c>
@@ -5639,7 +5575,7 @@
       </c>
       <c r="D199" s="6"/>
     </row>
-    <row r="200" spans="1:4">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A200" s="11" t="s">
         <v>113</v>
       </c>
@@ -5651,7 +5587,7 @@
       </c>
       <c r="D200" s="6"/>
     </row>
-    <row r="201" spans="1:4">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A201" s="11" t="s">
         <v>117</v>
       </c>
@@ -5663,7 +5599,7 @@
       </c>
       <c r="D201" s="6"/>
     </row>
-    <row r="202" spans="1:4">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A202" s="11" t="s">
         <v>121</v>
       </c>
@@ -5675,7 +5611,7 @@
       </c>
       <c r="D202" s="6"/>
     </row>
-    <row r="203" spans="1:4">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A203" s="11" t="s">
         <v>125</v>
       </c>
@@ -5687,7 +5623,7 @@
       </c>
       <c r="D203" s="6"/>
     </row>
-    <row r="204" spans="1:4">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A204" s="11" t="s">
         <v>129</v>
       </c>
@@ -5699,7 +5635,7 @@
       </c>
       <c r="D204" s="6"/>
     </row>
-    <row r="205" spans="1:4">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A205" s="11" t="s">
         <v>133</v>
       </c>
@@ -5711,7 +5647,7 @@
       </c>
       <c r="D205" s="6"/>
     </row>
-    <row r="206" spans="1:4">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A206" s="11" t="s">
         <v>137</v>
       </c>
@@ -5723,7 +5659,7 @@
       </c>
       <c r="D206" s="6"/>
     </row>
-    <row r="207" spans="1:4">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A207" s="11" t="s">
         <v>141</v>
       </c>
@@ -5735,7 +5671,7 @@
       </c>
       <c r="D207" s="6"/>
     </row>
-    <row r="208" spans="1:4">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A208" s="11" t="s">
         <v>145</v>
       </c>
@@ -5747,7 +5683,7 @@
       </c>
       <c r="D208" s="6"/>
     </row>
-    <row r="209" spans="1:4">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A209" s="11" t="s">
         <v>149</v>
       </c>
@@ -5759,7 +5695,7 @@
       </c>
       <c r="D209" s="6"/>
     </row>
-    <row r="210" spans="1:4">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A210" s="11" t="s">
         <v>158</v>
       </c>
@@ -5771,7 +5707,7 @@
       </c>
       <c r="D210" s="6"/>
     </row>
-    <row r="211" spans="1:4">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A211" s="11" t="s">
         <v>164</v>
       </c>
@@ -5783,7 +5719,7 @@
       </c>
       <c r="D211" s="6"/>
     </row>
-    <row r="212" spans="1:4">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A212" s="11" t="s">
         <v>170</v>
       </c>
@@ -5795,7 +5731,7 @@
       </c>
       <c r="D212" s="6"/>
     </row>
-    <row r="213" spans="1:4">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A213" s="11" t="s">
         <v>175</v>
       </c>
@@ -5807,7 +5743,7 @@
       </c>
       <c r="D213" s="6"/>
     </row>
-    <row r="214" spans="1:4">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A214" s="11" t="s">
         <v>179</v>
       </c>
@@ -5819,7 +5755,7 @@
       </c>
       <c r="D214" s="6"/>
     </row>
-    <row r="215" spans="1:4">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A215" s="11" t="s">
         <v>183</v>
       </c>
@@ -5831,7 +5767,7 @@
       </c>
       <c r="D215" s="6"/>
     </row>
-    <row r="216" spans="1:4">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A216" s="11" t="s">
         <v>187</v>
       </c>
@@ -5843,7 +5779,7 @@
       </c>
       <c r="D216" s="6"/>
     </row>
-    <row r="217" spans="1:4">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A217" s="11" t="s">
         <v>191</v>
       </c>
@@ -5855,7 +5791,7 @@
       </c>
       <c r="D217" s="6"/>
     </row>
-    <row r="218" spans="1:4">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A218" s="11" t="s">
         <v>195</v>
       </c>
@@ -5867,7 +5803,7 @@
       </c>
       <c r="D218" s="6"/>
     </row>
-    <row r="219" spans="1:4">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A219" s="11" t="s">
         <v>199</v>
       </c>
@@ -5879,7 +5815,7 @@
       </c>
       <c r="D219" s="6"/>
     </row>
-    <row r="220" spans="1:4">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A220" s="11" t="s">
         <v>203</v>
       </c>
@@ -5891,7 +5827,7 @@
       </c>
       <c r="D220" s="6"/>
     </row>
-    <row r="221" spans="1:4">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A221" s="11" t="s">
         <v>207</v>
       </c>
@@ -5903,7 +5839,7 @@
       </c>
       <c r="D221" s="6"/>
     </row>
-    <row r="222" spans="1:4">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A222" s="11" t="s">
         <v>216</v>
       </c>
@@ -5915,7 +5851,7 @@
       </c>
       <c r="D222" s="6"/>
     </row>
-    <row r="223" spans="1:4">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A223" s="11" t="s">
         <v>222</v>
       </c>
@@ -5927,7 +5863,7 @@
       </c>
       <c r="D223" s="6"/>
     </row>
-    <row r="224" spans="1:4">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A224" s="11" t="s">
         <v>228</v>
       </c>
@@ -5939,7 +5875,7 @@
       </c>
       <c r="D224" s="6"/>
     </row>
-    <row r="225" spans="1:4">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A225" s="11" t="s">
         <v>233</v>
       </c>
@@ -5951,7 +5887,7 @@
       </c>
       <c r="D225" s="6"/>
     </row>
-    <row r="226" spans="1:4">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A226" s="11" t="s">
         <v>237</v>
       </c>
@@ -5963,7 +5899,7 @@
       </c>
       <c r="D226" s="6"/>
     </row>
-    <row r="227" spans="1:4">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A227" s="11" t="s">
         <v>241</v>
       </c>
@@ -5975,7 +5911,7 @@
       </c>
       <c r="D227" s="6"/>
     </row>
-    <row r="228" spans="1:4">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A228" s="11" t="s">
         <v>245</v>
       </c>
@@ -5987,7 +5923,7 @@
       </c>
       <c r="D228" s="6"/>
     </row>
-    <row r="229" spans="1:4">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A229" s="11" t="s">
         <v>249</v>
       </c>
@@ -5999,7 +5935,7 @@
       </c>
       <c r="D229" s="6"/>
     </row>
-    <row r="230" spans="1:4">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A230" s="11" t="s">
         <v>253</v>
       </c>
@@ -6011,7 +5947,7 @@
       </c>
       <c r="D230" s="6"/>
     </row>
-    <row r="231" spans="1:4">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A231" s="11" t="s">
         <v>257</v>
       </c>
@@ -6023,7 +5959,7 @@
       </c>
       <c r="D231" s="6"/>
     </row>
-    <row r="232" spans="1:4">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A232" s="11" t="s">
         <v>261</v>
       </c>
@@ -6035,7 +5971,7 @@
       </c>
       <c r="D232" s="6"/>
     </row>
-    <row r="233" spans="1:4">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A233" s="11" t="s">
         <v>265</v>
       </c>
@@ -6047,7 +5983,7 @@
       </c>
       <c r="D233" s="6"/>
     </row>
-    <row r="234" spans="1:4">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A234" s="11" t="s">
         <v>274</v>
       </c>
@@ -6059,7 +5995,7 @@
       </c>
       <c r="D234" s="6"/>
     </row>
-    <row r="235" spans="1:4">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A235" s="11" t="s">
         <v>279</v>
       </c>
@@ -6071,7 +6007,7 @@
       </c>
       <c r="D235" s="6"/>
     </row>
-    <row r="236" spans="1:4">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A236" s="11" t="s">
         <v>284</v>
       </c>
@@ -6083,7 +6019,7 @@
       </c>
       <c r="D236" s="6"/>
     </row>
-    <row r="237" spans="1:4">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A237" s="11" t="s">
         <v>288</v>
       </c>
@@ -6095,7 +6031,7 @@
       </c>
       <c r="D237" s="6"/>
     </row>
-    <row r="238" spans="1:4">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A238" s="11" t="s">
         <v>291</v>
       </c>
@@ -6107,7 +6043,7 @@
       </c>
       <c r="D238" s="6"/>
     </row>
-    <row r="239" spans="1:4">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A239" s="11" t="s">
         <v>294</v>
       </c>
@@ -6119,7 +6055,7 @@
       </c>
       <c r="D239" s="6"/>
     </row>
-    <row r="240" spans="1:4">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A240" s="11" t="s">
         <v>297</v>
       </c>
@@ -6131,7 +6067,7 @@
       </c>
       <c r="D240" s="6"/>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A241" s="11" t="s">
         <v>300</v>
       </c>
@@ -6143,7 +6079,7 @@
       </c>
       <c r="D241" s="6"/>
     </row>
-    <row r="242" spans="1:4">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A242" s="11" t="s">
         <v>303</v>
       </c>
@@ -6155,7 +6091,7 @@
       </c>
       <c r="D242" s="6"/>
     </row>
-    <row r="243" spans="1:4">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A243" s="11" t="s">
         <v>306</v>
       </c>
@@ -6167,7 +6103,7 @@
       </c>
       <c r="D243" s="6"/>
     </row>
-    <row r="244" spans="1:4">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A244" s="11" t="s">
         <v>309</v>
       </c>
@@ -6179,7 +6115,7 @@
       </c>
       <c r="D244" s="6"/>
     </row>
-    <row r="245" spans="1:4">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A245" s="11" t="s">
         <v>312</v>
       </c>
@@ -6187,7 +6123,7 @@
       <c r="C245" s="64"/>
       <c r="D245" s="6"/>
     </row>
-    <row r="246" spans="1:4">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A246" s="11" t="s">
         <v>320</v>
       </c>
@@ -6199,7 +6135,7 @@
       </c>
       <c r="D246" s="6"/>
     </row>
-    <row r="247" spans="1:4">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A247" s="11" t="s">
         <v>325</v>
       </c>
@@ -6211,7 +6147,7 @@
       </c>
       <c r="D247" s="6"/>
     </row>
-    <row r="248" spans="1:4">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A248" s="11" t="s">
         <v>330</v>
       </c>
@@ -6223,7 +6159,7 @@
       </c>
       <c r="D248" s="6"/>
     </row>
-    <row r="249" spans="1:4">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A249" s="11" t="s">
         <v>334</v>
       </c>
@@ -6235,7 +6171,7 @@
       </c>
       <c r="D249" s="6"/>
     </row>
-    <row r="250" spans="1:4">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A250" s="11" t="s">
         <v>337</v>
       </c>
@@ -6247,7 +6183,7 @@
       </c>
       <c r="D250" s="6"/>
     </row>
-    <row r="251" spans="1:4">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A251" s="11" t="s">
         <v>340</v>
       </c>
@@ -6259,7 +6195,7 @@
       </c>
       <c r="D251" s="6"/>
     </row>
-    <row r="252" spans="1:4">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A252" s="11" t="s">
         <v>343</v>
       </c>
@@ -6271,7 +6207,7 @@
       </c>
       <c r="D252" s="6"/>
     </row>
-    <row r="253" spans="1:4">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A253" s="11" t="s">
         <v>346</v>
       </c>
@@ -6283,7 +6219,7 @@
       </c>
       <c r="D253" s="6"/>
     </row>
-    <row r="254" spans="1:4">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A254" s="11" t="s">
         <v>349</v>
       </c>
@@ -6295,7 +6231,7 @@
       </c>
       <c r="D254" s="6"/>
     </row>
-    <row r="255" spans="1:4">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A255" s="11" t="s">
         <v>352</v>
       </c>
@@ -6303,7 +6239,7 @@
       <c r="C255" s="64"/>
       <c r="D255" s="6"/>
     </row>
-    <row r="256" spans="1:4">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A256" s="11" t="s">
         <v>355</v>
       </c>
@@ -6311,7 +6247,7 @@
       <c r="C256" s="64"/>
       <c r="D256" s="6"/>
     </row>
-    <row r="257" spans="1:4">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A257" s="11" t="s">
         <v>358</v>
       </c>
@@ -6319,7 +6255,7 @@
       <c r="C257" s="64"/>
       <c r="D257" s="6"/>
     </row>
-    <row r="258" spans="1:4">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A258" s="11" t="s">
         <v>104</v>
       </c>
@@ -6331,7 +6267,7 @@
       </c>
       <c r="D258" s="6"/>
     </row>
-    <row r="259" spans="1:4">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A259" s="11" t="s">
         <v>109</v>
       </c>
@@ -6343,7 +6279,7 @@
       </c>
       <c r="D259" s="6"/>
     </row>
-    <row r="260" spans="1:4">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A260" s="11" t="s">
         <v>114</v>
       </c>
@@ -6355,7 +6291,7 @@
       </c>
       <c r="D260" s="6"/>
     </row>
-    <row r="261" spans="1:4">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A261" s="11" t="s">
         <v>118</v>
       </c>
@@ -6367,7 +6303,7 @@
       </c>
       <c r="D261" s="6"/>
     </row>
-    <row r="262" spans="1:4">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A262" s="11" t="s">
         <v>122</v>
       </c>
@@ -6379,7 +6315,7 @@
       </c>
       <c r="D262" s="6"/>
     </row>
-    <row r="263" spans="1:4">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A263" s="11" t="s">
         <v>126</v>
       </c>
@@ -6391,7 +6327,7 @@
       </c>
       <c r="D263" s="6"/>
     </row>
-    <row r="264" spans="1:4">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A264" s="11" t="s">
         <v>130</v>
       </c>
@@ -6403,7 +6339,7 @@
       </c>
       <c r="D264" s="6"/>
     </row>
-    <row r="265" spans="1:4">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A265" s="11" t="s">
         <v>134</v>
       </c>
@@ -6415,7 +6351,7 @@
       </c>
       <c r="D265" s="6"/>
     </row>
-    <row r="266" spans="1:4">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A266" s="11" t="s">
         <v>138</v>
       </c>
@@ -6427,7 +6363,7 @@
       </c>
       <c r="D266" s="6"/>
     </row>
-    <row r="267" spans="1:4">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A267" s="11" t="s">
         <v>142</v>
       </c>
@@ -6439,7 +6375,7 @@
       </c>
       <c r="D267" s="6"/>
     </row>
-    <row r="268" spans="1:4">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A268" s="11" t="s">
         <v>146</v>
       </c>
@@ -6451,7 +6387,7 @@
       </c>
       <c r="D268" s="6"/>
     </row>
-    <row r="269" spans="1:4">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A269" s="11" t="s">
         <v>150</v>
       </c>
@@ -6463,7 +6399,7 @@
       </c>
       <c r="D269" s="6"/>
     </row>
-    <row r="270" spans="1:4">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A270" s="11" t="s">
         <v>159</v>
       </c>
@@ -6475,7 +6411,7 @@
       </c>
       <c r="D270" s="6"/>
     </row>
-    <row r="271" spans="1:4">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A271" s="11" t="s">
         <v>165</v>
       </c>
@@ -6487,7 +6423,7 @@
       </c>
       <c r="D271" s="6"/>
     </row>
-    <row r="272" spans="1:4">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A272" s="11" t="s">
         <v>171</v>
       </c>
@@ -6499,7 +6435,7 @@
       </c>
       <c r="D272" s="6"/>
     </row>
-    <row r="273" spans="1:4">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A273" s="11" t="s">
         <v>176</v>
       </c>
@@ -6511,7 +6447,7 @@
       </c>
       <c r="D273" s="6"/>
     </row>
-    <row r="274" spans="1:4">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A274" s="11" t="s">
         <v>180</v>
       </c>
@@ -6523,7 +6459,7 @@
       </c>
       <c r="D274" s="6"/>
     </row>
-    <row r="275" spans="1:4">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A275" s="11" t="s">
         <v>184</v>
       </c>
@@ -6535,7 +6471,7 @@
       </c>
       <c r="D275" s="6"/>
     </row>
-    <row r="276" spans="1:4">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A276" s="11" t="s">
         <v>188</v>
       </c>
@@ -6547,7 +6483,7 @@
       </c>
       <c r="D276" s="6"/>
     </row>
-    <row r="277" spans="1:4">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A277" s="11" t="s">
         <v>192</v>
       </c>
@@ -6559,7 +6495,7 @@
       </c>
       <c r="D277" s="6"/>
     </row>
-    <row r="278" spans="1:4">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A278" s="11" t="s">
         <v>196</v>
       </c>
@@ -6571,7 +6507,7 @@
       </c>
       <c r="D278" s="6"/>
     </row>
-    <row r="279" spans="1:4">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A279" s="11" t="s">
         <v>200</v>
       </c>
@@ -6583,7 +6519,7 @@
       </c>
       <c r="D279" s="6"/>
     </row>
-    <row r="280" spans="1:4">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A280" s="11" t="s">
         <v>204</v>
       </c>
@@ -6595,7 +6531,7 @@
       </c>
       <c r="D280" s="6"/>
     </row>
-    <row r="281" spans="1:4">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A281" s="11" t="s">
         <v>208</v>
       </c>
@@ -6607,7 +6543,7 @@
       </c>
       <c r="D281" s="6"/>
     </row>
-    <row r="282" spans="1:4">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A282" s="11" t="s">
         <v>217</v>
       </c>
@@ -6619,7 +6555,7 @@
       </c>
       <c r="D282" s="6"/>
     </row>
-    <row r="283" spans="1:4">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A283" s="11" t="s">
         <v>223</v>
       </c>
@@ -6631,7 +6567,7 @@
       </c>
       <c r="D283" s="6"/>
     </row>
-    <row r="284" spans="1:4">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A284" s="11" t="s">
         <v>229</v>
       </c>
@@ -6643,7 +6579,7 @@
       </c>
       <c r="D284" s="6"/>
     </row>
-    <row r="285" spans="1:4">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A285" s="11" t="s">
         <v>234</v>
       </c>
@@ -6655,7 +6591,7 @@
       </c>
       <c r="D285" s="6"/>
     </row>
-    <row r="286" spans="1:4">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A286" s="11" t="s">
         <v>238</v>
       </c>
@@ -6667,7 +6603,7 @@
       </c>
       <c r="D286" s="6"/>
     </row>
-    <row r="287" spans="1:4">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A287" s="11" t="s">
         <v>242</v>
       </c>
@@ -6679,7 +6615,7 @@
       </c>
       <c r="D287" s="6"/>
     </row>
-    <row r="288" spans="1:4">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A288" s="11" t="s">
         <v>246</v>
       </c>
@@ -6691,7 +6627,7 @@
       </c>
       <c r="D288" s="6"/>
     </row>
-    <row r="289" spans="1:4">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A289" s="11" t="s">
         <v>250</v>
       </c>
@@ -6703,7 +6639,7 @@
       </c>
       <c r="D289" s="6"/>
     </row>
-    <row r="290" spans="1:4">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A290" s="11" t="s">
         <v>254</v>
       </c>
@@ -6715,7 +6651,7 @@
       </c>
       <c r="D290" s="6"/>
     </row>
-    <row r="291" spans="1:4">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A291" s="11" t="s">
         <v>258</v>
       </c>
@@ -6727,7 +6663,7 @@
       </c>
       <c r="D291" s="6"/>
     </row>
-    <row r="292" spans="1:4">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A292" s="11" t="s">
         <v>262</v>
       </c>
@@ -6739,7 +6675,7 @@
       </c>
       <c r="D292" s="6"/>
     </row>
-    <row r="293" spans="1:4">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A293" s="11" t="s">
         <v>266</v>
       </c>
@@ -6751,7 +6687,7 @@
       </c>
       <c r="D293" s="6"/>
     </row>
-    <row r="294" spans="1:4">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A294" s="11" t="s">
         <v>151</v>
       </c>
@@ -6763,7 +6699,7 @@
       </c>
       <c r="D294" s="6"/>
     </row>
-    <row r="295" spans="1:4">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A295" s="11" t="s">
         <v>209</v>
       </c>
@@ -6775,7 +6711,7 @@
       </c>
       <c r="D295" s="6"/>
     </row>
-    <row r="296" spans="1:4">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A296" s="11" t="s">
         <v>267</v>
       </c>
@@ -6787,7 +6723,7 @@
       </c>
       <c r="D296" s="6"/>
     </row>
-    <row r="297" spans="1:4">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A297" s="11" t="s">
         <v>313</v>
       </c>
@@ -6799,7 +6735,7 @@
       </c>
       <c r="D297" s="6"/>
     </row>
-    <row r="298" spans="1:4">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A298" s="11" t="s">
         <v>359</v>
       </c>
@@ -6811,7 +6747,7 @@
       </c>
       <c r="D298" s="6"/>
     </row>
-    <row r="299" spans="1:4">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A299" s="11" t="s">
         <v>369</v>
       </c>
@@ -6823,7 +6759,7 @@
       </c>
       <c r="D299" s="6"/>
     </row>
-    <row r="300" spans="1:4">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A300" s="11" t="s">
         <v>379</v>
       </c>
@@ -6835,7 +6771,7 @@
       </c>
       <c r="D300" s="6"/>
     </row>
-    <row r="301" spans="1:4">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A301" s="11" t="s">
         <v>389</v>
       </c>
@@ -6847,7 +6783,7 @@
       </c>
       <c r="D301" s="6"/>
     </row>
-    <row r="302" spans="1:4">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A302" s="11" t="s">
         <v>399</v>
       </c>
@@ -6859,7 +6795,7 @@
       </c>
       <c r="D302" s="6"/>
     </row>
-    <row r="303" spans="1:4">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A303" s="11" t="s">
         <v>409</v>
       </c>
@@ -6871,7 +6807,7 @@
       </c>
       <c r="D303" s="6"/>
     </row>
-    <row r="304" spans="1:4">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A304" s="11" t="s">
         <v>419</v>
       </c>
@@ -6883,7 +6819,7 @@
       </c>
       <c r="D304" s="6"/>
     </row>
-    <row r="305" spans="1:4">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A305" s="11" t="s">
         <v>429</v>
       </c>
@@ -6895,7 +6831,7 @@
       </c>
       <c r="D305" s="6"/>
     </row>
-    <row r="306" spans="1:4">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A306" s="11" t="s">
         <v>439</v>
       </c>
@@ -6907,7 +6843,7 @@
       </c>
       <c r="D306" s="6"/>
     </row>
-    <row r="307" spans="1:4">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A307" s="11" t="s">
         <v>449</v>
       </c>
@@ -6919,7 +6855,7 @@
       </c>
       <c r="D307" s="6"/>
     </row>
-    <row r="308" spans="1:4">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A308" s="11" t="s">
         <v>459</v>
       </c>
@@ -6931,7 +6867,7 @@
       </c>
       <c r="D308" s="6"/>
     </row>
-    <row r="309" spans="1:4">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A309" s="11" t="s">
         <v>469</v>
       </c>
@@ -6943,7 +6879,7 @@
       </c>
       <c r="D309" s="6"/>
     </row>
-    <row r="310" spans="1:4">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A310" s="11" t="s">
         <v>477</v>
       </c>
@@ -6955,7 +6891,7 @@
       </c>
       <c r="D310" s="6"/>
     </row>
-    <row r="311" spans="1:4">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A311" s="11" t="s">
         <v>485</v>
       </c>
@@ -6967,7 +6903,7 @@
       </c>
       <c r="D311" s="6"/>
     </row>
-    <row r="312" spans="1:4">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A312" s="11" t="s">
         <v>492</v>
       </c>
@@ -6979,7 +6915,7 @@
       </c>
       <c r="D312" s="6"/>
     </row>
-    <row r="313" spans="1:4">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A313" s="11" t="s">
         <v>154</v>
       </c>
@@ -6991,7 +6927,7 @@
       </c>
       <c r="D313" s="6"/>
     </row>
-    <row r="314" spans="1:4">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A314" s="11" t="s">
         <v>160</v>
       </c>
@@ -7003,7 +6939,7 @@
       </c>
       <c r="D314" s="6"/>
     </row>
-    <row r="315" spans="1:4">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A315" s="11" t="s">
         <v>166</v>
       </c>
@@ -7015,7 +6951,7 @@
       </c>
       <c r="D315" s="6"/>
     </row>
-    <row r="316" spans="1:4">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A316" s="11" t="s">
         <v>172</v>
       </c>
@@ -7027,7 +6963,7 @@
       </c>
       <c r="D316" s="6"/>
     </row>
-    <row r="317" spans="1:4">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A317" s="11" t="s">
         <v>212</v>
       </c>
@@ -7039,7 +6975,7 @@
       </c>
       <c r="D317" s="6"/>
     </row>
-    <row r="318" spans="1:4">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A318" s="11" t="s">
         <v>218</v>
       </c>
@@ -7051,7 +6987,7 @@
       </c>
       <c r="D318" s="6"/>
     </row>
-    <row r="319" spans="1:4">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A319" s="11" t="s">
         <v>224</v>
       </c>
@@ -7063,7 +6999,7 @@
       </c>
       <c r="D319" s="6"/>
     </row>
-    <row r="320" spans="1:4">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A320" s="11" t="s">
         <v>230</v>
       </c>
@@ -7075,7 +7011,7 @@
       </c>
       <c r="D320" s="6"/>
     </row>
-    <row r="321" spans="1:4">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A321" s="11" t="s">
         <v>270</v>
       </c>
@@ -7087,7 +7023,7 @@
       </c>
       <c r="D321" s="6"/>
     </row>
-    <row r="322" spans="1:4">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A322" s="11" t="s">
         <v>275</v>
       </c>
@@ -7099,7 +7035,7 @@
       </c>
       <c r="D322" s="6"/>
     </row>
-    <row r="323" spans="1:4">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A323" s="11" t="s">
         <v>280</v>
       </c>
@@ -7111,7 +7047,7 @@
       </c>
       <c r="D323" s="6"/>
     </row>
-    <row r="324" spans="1:4">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A324" s="11" t="s">
         <v>285</v>
       </c>
@@ -7123,7 +7059,7 @@
       </c>
       <c r="D324" s="6"/>
     </row>
-    <row r="325" spans="1:4">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A325" s="11" t="s">
         <v>316</v>
       </c>
@@ -7135,7 +7071,7 @@
       </c>
       <c r="D325" s="6"/>
     </row>
-    <row r="326" spans="1:4">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A326" s="11" t="s">
         <v>321</v>
       </c>
@@ -7147,7 +7083,7 @@
       </c>
       <c r="D326" s="6"/>
     </row>
-    <row r="327" spans="1:4">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A327" s="11" t="s">
         <v>326</v>
       </c>
@@ -7159,7 +7095,7 @@
       </c>
       <c r="D327" s="6"/>
     </row>
-    <row r="328" spans="1:4">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A328" s="11" t="s">
         <v>331</v>
       </c>
@@ -7171,7 +7107,7 @@
       </c>
       <c r="D328" s="6"/>
     </row>
-    <row r="329" spans="1:4">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A329" s="11" t="s">
         <v>362</v>
       </c>
@@ -7183,7 +7119,7 @@
       </c>
       <c r="D329" s="6"/>
     </row>
-    <row r="330" spans="1:4">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A330" s="11" t="s">
         <v>364</v>
       </c>
@@ -7195,7 +7131,7 @@
       </c>
       <c r="D330" s="6"/>
     </row>
-    <row r="331" spans="1:4">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A331" s="11" t="s">
         <v>366</v>
       </c>
@@ -7207,7 +7143,7 @@
       </c>
       <c r="D331" s="6"/>
     </row>
-    <row r="332" spans="1:4">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A332" s="11" t="s">
         <v>368</v>
       </c>
@@ -7219,7 +7155,7 @@
       </c>
       <c r="D332" s="6"/>
     </row>
-    <row r="333" spans="1:4">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A333" s="11" t="s">
         <v>372</v>
       </c>
@@ -7231,7 +7167,7 @@
       </c>
       <c r="D333" s="6"/>
     </row>
-    <row r="334" spans="1:4">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A334" s="11" t="s">
         <v>374</v>
       </c>
@@ -7243,7 +7179,7 @@
       </c>
       <c r="D334" s="6"/>
     </row>
-    <row r="335" spans="1:4">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A335" s="11" t="s">
         <v>376</v>
       </c>
@@ -7255,7 +7191,7 @@
       </c>
       <c r="D335" s="6"/>
     </row>
-    <row r="336" spans="1:4">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A336" s="11" t="s">
         <v>378</v>
       </c>
@@ -7267,7 +7203,7 @@
       </c>
       <c r="D336" s="6"/>
     </row>
-    <row r="337" spans="1:4">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A337" s="11" t="s">
         <v>382</v>
       </c>
@@ -7279,7 +7215,7 @@
       </c>
       <c r="D337" s="6"/>
     </row>
-    <row r="338" spans="1:4">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A338" s="11" t="s">
         <v>384</v>
       </c>
@@ -7291,7 +7227,7 @@
       </c>
       <c r="D338" s="6"/>
     </row>
-    <row r="339" spans="1:4">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A339" s="11" t="s">
         <v>386</v>
       </c>
@@ -7303,7 +7239,7 @@
       </c>
       <c r="D339" s="6"/>
     </row>
-    <row r="340" spans="1:4">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A340" s="11" t="s">
         <v>388</v>
       </c>
@@ -7315,7 +7251,7 @@
       </c>
       <c r="D340" s="6"/>
     </row>
-    <row r="341" spans="1:4">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A341" s="11" t="s">
         <v>392</v>
       </c>
@@ -7327,7 +7263,7 @@
       </c>
       <c r="D341" s="6"/>
     </row>
-    <row r="342" spans="1:4">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A342" s="11" t="s">
         <v>394</v>
       </c>
@@ -7339,7 +7275,7 @@
       </c>
       <c r="D342" s="6"/>
     </row>
-    <row r="343" spans="1:4">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A343" s="11" t="s">
         <v>396</v>
       </c>
@@ -7351,7 +7287,7 @@
       </c>
       <c r="D343" s="6"/>
     </row>
-    <row r="344" spans="1:4">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A344" s="11" t="s">
         <v>398</v>
       </c>
@@ -7363,7 +7299,7 @@
       </c>
       <c r="D344" s="6"/>
     </row>
-    <row r="345" spans="1:4">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A345" s="11" t="s">
         <v>402</v>
       </c>
@@ -7375,7 +7311,7 @@
       </c>
       <c r="D345" s="6"/>
     </row>
-    <row r="346" spans="1:4">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A346" s="11" t="s">
         <v>404</v>
       </c>
@@ -7387,7 +7323,7 @@
       </c>
       <c r="D346" s="6"/>
     </row>
-    <row r="347" spans="1:4">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A347" s="11" t="s">
         <v>406</v>
       </c>
@@ -7399,7 +7335,7 @@
       </c>
       <c r="D347" s="6"/>
     </row>
-    <row r="348" spans="1:4">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A348" s="11" t="s">
         <v>408</v>
       </c>
@@ -7411,7 +7347,7 @@
       </c>
       <c r="D348" s="6"/>
     </row>
-    <row r="349" spans="1:4">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A349" s="11" t="s">
         <v>412</v>
       </c>
@@ -7423,7 +7359,7 @@
       </c>
       <c r="D349" s="6"/>
     </row>
-    <row r="350" spans="1:4">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A350" s="11" t="s">
         <v>414</v>
       </c>
@@ -7435,7 +7371,7 @@
       </c>
       <c r="D350" s="6"/>
     </row>
-    <row r="351" spans="1:4">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A351" s="11" t="s">
         <v>416</v>
       </c>
@@ -7447,7 +7383,7 @@
       </c>
       <c r="D351" s="6"/>
     </row>
-    <row r="352" spans="1:4">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A352" s="11" t="s">
         <v>418</v>
       </c>
@@ -7459,7 +7395,7 @@
       </c>
       <c r="D352" s="6"/>
     </row>
-    <row r="353" spans="1:4">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A353" s="11" t="s">
         <v>422</v>
       </c>
@@ -7471,7 +7407,7 @@
       </c>
       <c r="D353" s="6"/>
     </row>
-    <row r="354" spans="1:4">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A354" s="11" t="s">
         <v>424</v>
       </c>
@@ -7483,7 +7419,7 @@
       </c>
       <c r="D354" s="6"/>
     </row>
-    <row r="355" spans="1:4">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A355" s="11" t="s">
         <v>426</v>
       </c>
@@ -7495,7 +7431,7 @@
       </c>
       <c r="D355" s="6"/>
     </row>
-    <row r="356" spans="1:4">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A356" s="11" t="s">
         <v>428</v>
       </c>
@@ -7507,7 +7443,7 @@
       </c>
       <c r="D356" s="6"/>
     </row>
-    <row r="357" spans="1:4">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A357" s="11" t="s">
         <v>432</v>
       </c>
@@ -7519,7 +7455,7 @@
       </c>
       <c r="D357" s="6"/>
     </row>
-    <row r="358" spans="1:4">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A358" s="11" t="s">
         <v>434</v>
       </c>
@@ -7531,7 +7467,7 @@
       </c>
       <c r="D358" s="6"/>
     </row>
-    <row r="359" spans="1:4">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A359" s="11" t="s">
         <v>436</v>
       </c>
@@ -7543,7 +7479,7 @@
       </c>
       <c r="D359" s="6"/>
     </row>
-    <row r="360" spans="1:4">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A360" s="11" t="s">
         <v>438</v>
       </c>
@@ -7555,7 +7491,7 @@
       </c>
       <c r="D360" s="6"/>
     </row>
-    <row r="361" spans="1:4">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A361" s="11" t="s">
         <v>442</v>
       </c>
@@ -7567,7 +7503,7 @@
       </c>
       <c r="D361" s="6"/>
     </row>
-    <row r="362" spans="1:4">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A362" s="11" t="s">
         <v>444</v>
       </c>
@@ -7579,7 +7515,7 @@
       </c>
       <c r="D362" s="6"/>
     </row>
-    <row r="363" spans="1:4">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A363" s="11" t="s">
         <v>446</v>
       </c>
@@ -7591,7 +7527,7 @@
       </c>
       <c r="D363" s="6"/>
     </row>
-    <row r="364" spans="1:4">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A364" s="11" t="s">
         <v>448</v>
       </c>
@@ -7603,7 +7539,7 @@
       </c>
       <c r="D364" s="6"/>
     </row>
-    <row r="365" spans="1:4">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A365" s="11" t="s">
         <v>452</v>
       </c>
@@ -7615,7 +7551,7 @@
       </c>
       <c r="D365" s="6"/>
     </row>
-    <row r="366" spans="1:4">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A366" s="11" t="s">
         <v>454</v>
       </c>
@@ -7627,7 +7563,7 @@
       </c>
       <c r="D366" s="6"/>
     </row>
-    <row r="367" spans="1:4">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A367" s="11" t="s">
         <v>456</v>
       </c>
@@ -7639,7 +7575,7 @@
       </c>
       <c r="D367" s="6"/>
     </row>
-    <row r="368" spans="1:4">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A368" s="11" t="s">
         <v>458</v>
       </c>
@@ -7651,7 +7587,7 @@
       </c>
       <c r="D368" s="6"/>
     </row>
-    <row r="369" spans="1:4">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A369" s="11" t="s">
         <v>462</v>
       </c>
@@ -7663,7 +7599,7 @@
       </c>
       <c r="D369" s="6"/>
     </row>
-    <row r="370" spans="1:4">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A370" s="11" t="s">
         <v>464</v>
       </c>
@@ -7675,7 +7611,7 @@
       </c>
       <c r="D370" s="6"/>
     </row>
-    <row r="371" spans="1:4">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A371" s="11" t="s">
         <v>466</v>
       </c>
@@ -7687,7 +7623,7 @@
       </c>
       <c r="D371" s="6"/>
     </row>
-    <row r="372" spans="1:4">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A372" s="11" t="s">
         <v>468</v>
       </c>
@@ -7699,7 +7635,7 @@
       </c>
       <c r="D372" s="6"/>
     </row>
-    <row r="373" spans="1:4">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A373" s="11" t="s">
         <v>472</v>
       </c>
@@ -7711,7 +7647,7 @@
       </c>
       <c r="D373" s="6"/>
     </row>
-    <row r="374" spans="1:4">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A374" s="11" t="s">
         <v>474</v>
       </c>
@@ -7719,7 +7655,7 @@
       <c r="C374" s="64"/>
       <c r="D374" s="6"/>
     </row>
-    <row r="375" spans="1:4">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A375" s="11" t="s">
         <v>480</v>
       </c>
@@ -7731,7 +7667,7 @@
       </c>
       <c r="D375" s="6"/>
     </row>
-    <row r="376" spans="1:4">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A376" s="11" t="s">
         <v>482</v>
       </c>
@@ -7739,7 +7675,7 @@
       <c r="C376" s="64"/>
       <c r="D376" s="6"/>
     </row>
-    <row r="377" spans="1:4">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A377" s="11" t="s">
         <v>487</v>
       </c>
@@ -7751,7 +7687,7 @@
       </c>
       <c r="D377" s="6"/>
     </row>
-    <row r="378" spans="1:4">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A378" s="11" t="s">
         <v>489</v>
       </c>
@@ -7759,7 +7695,7 @@
       <c r="C378" s="64"/>
       <c r="D378" s="6"/>
     </row>
-    <row r="379" spans="1:4">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A379" s="11" t="s">
         <v>152</v>
       </c>
@@ -7771,7 +7707,7 @@
       </c>
       <c r="D379" s="6"/>
     </row>
-    <row r="380" spans="1:4">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A380" s="11" t="s">
         <v>210</v>
       </c>
@@ -7783,7 +7719,7 @@
       </c>
       <c r="D380" s="6"/>
     </row>
-    <row r="381" spans="1:4">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A381" s="11" t="s">
         <v>268</v>
       </c>
@@ -7795,7 +7731,7 @@
       </c>
       <c r="D381" s="6"/>
     </row>
-    <row r="382" spans="1:4">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A382" s="11" t="s">
         <v>314</v>
       </c>
@@ -7807,7 +7743,7 @@
       </c>
       <c r="D382" s="6"/>
     </row>
-    <row r="383" spans="1:4">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A383" s="11" t="s">
         <v>360</v>
       </c>
@@ -7819,7 +7755,7 @@
       </c>
       <c r="D383" s="6"/>
     </row>
-    <row r="384" spans="1:4">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A384" s="11" t="s">
         <v>370</v>
       </c>
@@ -7831,7 +7767,7 @@
       </c>
       <c r="D384" s="6"/>
     </row>
-    <row r="385" spans="1:4">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A385" s="11" t="s">
         <v>380</v>
       </c>
@@ -7843,7 +7779,7 @@
       </c>
       <c r="D385" s="6"/>
     </row>
-    <row r="386" spans="1:4">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A386" s="11" t="s">
         <v>390</v>
       </c>
@@ -7855,7 +7791,7 @@
       </c>
       <c r="D386" s="6"/>
     </row>
-    <row r="387" spans="1:4">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A387" s="11" t="s">
         <v>400</v>
       </c>
@@ -7867,7 +7803,7 @@
       </c>
       <c r="D387" s="6"/>
     </row>
-    <row r="388" spans="1:4">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A388" s="11" t="s">
         <v>410</v>
       </c>
@@ -7879,7 +7815,7 @@
       </c>
       <c r="D388" s="6"/>
     </row>
-    <row r="389" spans="1:4">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A389" s="11" t="s">
         <v>420</v>
       </c>
@@ -7891,7 +7827,7 @@
       </c>
       <c r="D389" s="6"/>
     </row>
-    <row r="390" spans="1:4">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A390" s="11" t="s">
         <v>430</v>
       </c>
@@ -7903,7 +7839,7 @@
       </c>
       <c r="D390" s="6"/>
     </row>
-    <row r="391" spans="1:4">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A391" s="11" t="s">
         <v>440</v>
       </c>
@@ -7915,7 +7851,7 @@
       </c>
       <c r="D391" s="6"/>
     </row>
-    <row r="392" spans="1:4">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A392" s="11" t="s">
         <v>450</v>
       </c>
@@ -7927,7 +7863,7 @@
       </c>
       <c r="D392" s="6"/>
     </row>
-    <row r="393" spans="1:4">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A393" s="11" t="s">
         <v>460</v>
       </c>
@@ -7939,7 +7875,7 @@
       </c>
       <c r="D393" s="6"/>
     </row>
-    <row r="394" spans="1:4">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A394" s="11" t="s">
         <v>470</v>
       </c>
@@ -7951,7 +7887,7 @@
       </c>
       <c r="D394" s="1"/>
     </row>
-    <row r="395" spans="1:4">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A395" s="11" t="s">
         <v>478</v>
       </c>
@@ -7963,19 +7899,19 @@
       </c>
       <c r="D395" s="1"/>
     </row>
-    <row r="396" spans="1:4">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A396" s="11"/>
       <c r="B396" s="11"/>
       <c r="C396" s="64"/>
       <c r="D396" s="1"/>
     </row>
-    <row r="397" spans="1:4">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A397" s="11"/>
       <c r="B397" s="11"/>
       <c r="C397" s="64"/>
       <c r="D397" s="1"/>
     </row>
-    <row r="398" spans="1:4">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A398" s="11" t="s">
         <v>64</v>
       </c>
@@ -7987,7 +7923,7 @@
       </c>
       <c r="D398" s="1"/>
     </row>
-    <row r="399" spans="1:4">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A399" s="11" t="s">
         <v>63</v>
       </c>
@@ -7999,7 +7935,7 @@
       </c>
       <c r="D399" s="1"/>
     </row>
-    <row r="400" spans="1:4">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A400" s="11" t="s">
         <v>65</v>
       </c>
@@ -8011,86 +7947,86 @@
       </c>
       <c r="D400" s="1"/>
     </row>
-    <row r="401" spans="1:4">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A401" s="11"/>
       <c r="B401" s="11"/>
       <c r="C401" s="64"/>
       <c r="D401" s="1"/>
     </row>
-    <row r="402" spans="1:4">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A402" s="11"/>
       <c r="B402" s="11"/>
       <c r="C402" s="64"/>
       <c r="D402" s="1"/>
     </row>
-    <row r="403" spans="1:4">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A403" s="11"/>
       <c r="B403" s="11"/>
       <c r="C403" s="64"/>
       <c r="D403" s="1"/>
     </row>
-    <row r="404" spans="1:4">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A404" s="11"/>
       <c r="B404" s="11"/>
       <c r="C404" s="64"/>
       <c r="D404" s="1"/>
     </row>
-    <row r="405" spans="1:4">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A405" s="11"/>
       <c r="B405" s="11"/>
       <c r="C405" s="64"/>
       <c r="D405" s="1"/>
     </row>
-    <row r="406" spans="1:4">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A406" s="11"/>
       <c r="B406" s="11"/>
       <c r="C406" s="64"/>
       <c r="D406" s="1"/>
     </row>
-    <row r="407" spans="1:4">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A407" s="11"/>
       <c r="B407" s="11"/>
       <c r="C407" s="64"/>
       <c r="D407" s="1"/>
     </row>
-    <row r="408" spans="1:4">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A408" s="11"/>
       <c r="B408" s="11"/>
       <c r="C408" s="64"/>
       <c r="D408" s="1"/>
     </row>
-    <row r="409" spans="1:4">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A409" s="11"/>
       <c r="B409" s="11"/>
       <c r="C409" s="64"/>
       <c r="D409" s="1"/>
     </row>
-    <row r="410" spans="1:4">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A410" s="11"/>
       <c r="B410" s="11"/>
       <c r="C410" s="64"/>
       <c r="D410" s="1"/>
     </row>
-    <row r="411" spans="1:4">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A411" s="11"/>
       <c r="B411" s="11"/>
       <c r="C411" s="64"/>
       <c r="D411" s="1"/>
     </row>
-    <row r="412" spans="1:4">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A412" s="11"/>
       <c r="B412" s="11"/>
       <c r="C412" s="64"/>
       <c r="D412" s="1"/>
     </row>
-    <row r="413" spans="1:4">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A413" s="11"/>
       <c r="B413" s="11"/>
       <c r="C413" s="64"/>
       <c r="D413" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C413">
+  <sortState ref="A2:C413">
     <sortCondition ref="A2:A413"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -8100,19 +8036,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{020C681C-7B39-46D7-97F2-912BB2ED1277}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:F56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.8" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="9" style="4"/>
     <col min="4" max="4" width="5" style="4" customWidth="1"/>
     <col min="5" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="51" t="s">
         <v>66</v>
       </c>
@@ -8124,7 +8060,7 @@
       </c>
       <c r="D1" s="53"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="54" t="s">
         <v>55</v>
       </c>
@@ -8136,7 +8072,7 @@
       </c>
       <c r="D2" s="56"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="54" t="s">
         <v>55</v>
       </c>
@@ -8148,7 +8084,7 @@
       </c>
       <c r="D3" s="56"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="54" t="s">
         <v>55</v>
       </c>
@@ -8160,7 +8096,7 @@
       </c>
       <c r="D4" s="56"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="54" t="s">
         <v>55</v>
       </c>
@@ -8172,7 +8108,7 @@
       </c>
       <c r="D5" s="56"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="54" t="s">
         <v>55</v>
       </c>
@@ -8186,7 +8122,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="54" t="s">
         <v>55</v>
       </c>
@@ -8198,7 +8134,7 @@
       </c>
       <c r="D7" s="56"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="54" t="s">
         <v>55</v>
       </c>
@@ -8210,7 +8146,7 @@
       </c>
       <c r="D8" s="56"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="54" t="s">
         <v>55</v>
       </c>
@@ -8222,7 +8158,7 @@
       </c>
       <c r="D9" s="56"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="54" t="s">
         <v>55</v>
       </c>
@@ -8234,7 +8170,7 @@
       </c>
       <c r="D10" s="56"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="54" t="s">
         <v>55</v>
       </c>
@@ -8246,7 +8182,7 @@
       </c>
       <c r="D11" s="56"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="57" t="s">
         <v>56</v>
       </c>
@@ -8258,7 +8194,7 @@
       </c>
       <c r="D12" s="59"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="57" t="s">
         <v>56</v>
       </c>
@@ -8270,7 +8206,7 @@
       </c>
       <c r="D13" s="59"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="57" t="s">
         <v>56</v>
       </c>
@@ -8282,7 +8218,7 @@
       </c>
       <c r="D14" s="59"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="57" t="s">
         <v>56</v>
       </c>
@@ -8294,7 +8230,7 @@
       </c>
       <c r="D15" s="59"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="57" t="s">
         <v>56</v>
       </c>
@@ -8306,7 +8242,7 @@
       </c>
       <c r="D16" s="59"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="54" t="s">
         <v>57</v>
       </c>
@@ -8318,7 +8254,7 @@
       </c>
       <c r="D17" s="56"/>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="54" t="s">
         <v>57</v>
       </c>
@@ -8330,7 +8266,7 @@
       </c>
       <c r="D18" s="56"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="54" t="s">
         <v>57</v>
       </c>
@@ -8342,7 +8278,7 @@
       </c>
       <c r="D19" s="56"/>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="54" t="s">
         <v>57</v>
       </c>
@@ -8354,7 +8290,7 @@
       </c>
       <c r="D20" s="56"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="54" t="s">
         <v>57</v>
       </c>
@@ -8366,7 +8302,7 @@
       </c>
       <c r="D21" s="56"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="54" t="s">
         <v>57</v>
       </c>
@@ -8378,7 +8314,7 @@
       </c>
       <c r="D22" s="56"/>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="54" t="s">
         <v>57</v>
       </c>
@@ -8390,7 +8326,7 @@
       </c>
       <c r="D23" s="56"/>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="54" t="s">
         <v>57</v>
       </c>
@@ -8402,7 +8338,7 @@
       </c>
       <c r="D24" s="56"/>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="54" t="s">
         <v>57</v>
       </c>
@@ -8414,7 +8350,7 @@
       </c>
       <c r="D25" s="56"/>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="54" t="s">
         <v>57</v>
       </c>
@@ -8426,7 +8362,7 @@
       </c>
       <c r="D26" s="56"/>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="57" t="s">
         <v>58</v>
       </c>
@@ -8438,7 +8374,7 @@
       </c>
       <c r="D27" s="59"/>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="57" t="s">
         <v>58</v>
       </c>
@@ -8450,7 +8386,7 @@
       </c>
       <c r="D28" s="59"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="57" t="s">
         <v>58</v>
       </c>
@@ -8462,7 +8398,7 @@
       </c>
       <c r="D29" s="59"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="57" t="s">
         <v>58</v>
       </c>
@@ -8474,7 +8410,7 @@
       </c>
       <c r="D30" s="59"/>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="57" t="s">
         <v>58</v>
       </c>
@@ -8486,7 +8422,7 @@
       </c>
       <c r="D31" s="59"/>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="57" t="s">
         <v>58</v>
       </c>
@@ -8498,7 +8434,7 @@
       </c>
       <c r="D32" s="59"/>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="57" t="s">
         <v>58</v>
       </c>
@@ -8510,7 +8446,7 @@
       </c>
       <c r="D33" s="59"/>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="57" t="s">
         <v>58</v>
       </c>
@@ -8522,7 +8458,7 @@
       </c>
       <c r="D34" s="59"/>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="57" t="s">
         <v>58</v>
       </c>
@@ -8534,7 +8470,7 @@
       </c>
       <c r="D35" s="59"/>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="57" t="s">
         <v>58</v>
       </c>
@@ -8546,7 +8482,7 @@
       </c>
       <c r="D36" s="59"/>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="57" t="s">
         <v>58</v>
       </c>
@@ -8558,7 +8494,7 @@
       </c>
       <c r="D37" s="59"/>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="57" t="s">
         <v>58</v>
       </c>
@@ -8570,7 +8506,7 @@
       </c>
       <c r="D38" s="59"/>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="54" t="s">
         <v>59</v>
       </c>
@@ -8582,7 +8518,7 @@
       </c>
       <c r="D39" s="56"/>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="54" t="s">
         <v>59</v>
       </c>
@@ -8594,7 +8530,7 @@
       </c>
       <c r="D40" s="56"/>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="54" t="s">
         <v>59</v>
       </c>
@@ -8606,7 +8542,7 @@
       </c>
       <c r="D41" s="56"/>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="54" t="s">
         <v>59</v>
       </c>
@@ -8618,7 +8554,7 @@
       </c>
       <c r="D42" s="56"/>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="54" t="s">
         <v>59</v>
       </c>
@@ -8630,7 +8566,7 @@
       </c>
       <c r="D43" s="56"/>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="54" t="s">
         <v>59</v>
       </c>
@@ -8642,7 +8578,7 @@
       </c>
       <c r="D44" s="56"/>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="54" t="s">
         <v>59</v>
       </c>
@@ -8654,7 +8590,7 @@
       </c>
       <c r="D45" s="56"/>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="54" t="s">
         <v>59</v>
       </c>
@@ -8666,7 +8602,7 @@
       </c>
       <c r="D46" s="56"/>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="54" t="s">
         <v>59</v>
       </c>
@@ -8678,7 +8614,7 @@
       </c>
       <c r="D47" s="56"/>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="57" t="s">
         <v>60</v>
       </c>
@@ -8690,7 +8626,7 @@
       </c>
       <c r="D48" s="59"/>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" s="57" t="s">
         <v>60</v>
       </c>
@@ -8702,7 +8638,7 @@
       </c>
       <c r="D49" s="59"/>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="57" t="s">
         <v>60</v>
       </c>
@@ -8714,7 +8650,7 @@
       </c>
       <c r="D50" s="59"/>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" s="57" t="s">
         <v>60</v>
       </c>
@@ -8726,7 +8662,7 @@
       </c>
       <c r="D51" s="59"/>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="57" t="s">
         <v>60</v>
       </c>
@@ -8738,7 +8674,7 @@
       </c>
       <c r="D52" s="59"/>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="57" t="s">
         <v>60</v>
       </c>
@@ -8750,7 +8686,7 @@
       </c>
       <c r="D53" s="59"/>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" s="57" t="s">
         <v>60</v>
       </c>
@@ -8762,7 +8698,7 @@
       </c>
       <c r="D54" s="59"/>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" s="57" t="s">
         <v>60</v>
       </c>
@@ -8774,7 +8710,7 @@
       </c>
       <c r="D55" s="59"/>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" s="57" t="s">
         <v>60</v>
       </c>
@@ -8794,32 +8730,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE943C2B-D5A8-41BC-A279-879F4621BD22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet22">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:AQ376"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.75" style="1" customWidth="1"/>
-    <col min="2" max="19" width="6.125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="10.625" style="93" customWidth="1"/>
-    <col min="21" max="21" width="8.5" style="1" customWidth="1"/>
-    <col min="22" max="23" width="6.125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="3.875" style="1" customWidth="1"/>
-    <col min="25" max="26" width="10.75" style="1" customWidth="1"/>
-    <col min="27" max="27" width="3.875" style="1" customWidth="1"/>
-    <col min="28" max="30" width="6.5" style="1" customWidth="1"/>
-    <col min="31" max="31" width="3.875" style="1" customWidth="1"/>
-    <col min="32" max="34" width="5.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" style="1" customWidth="1"/>
+    <col min="2" max="19" width="6.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="10.6640625" style="93" customWidth="1"/>
+    <col min="21" max="21" width="8.44140625" style="1" customWidth="1"/>
+    <col min="22" max="23" width="6.109375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="3.88671875" style="1" customWidth="1"/>
+    <col min="25" max="26" width="10.77734375" style="1" customWidth="1"/>
+    <col min="27" max="27" width="3.88671875" style="1" customWidth="1"/>
+    <col min="28" max="30" width="6.44140625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="3.88671875" style="1" customWidth="1"/>
+    <col min="32" max="34" width="5.44140625" style="1" customWidth="1"/>
     <col min="35" max="35" width="9" style="1"/>
-    <col min="36" max="36" width="11.375" style="1" customWidth="1"/>
-    <col min="37" max="42" width="7.25" style="1" customWidth="1"/>
-    <col min="43" max="43" width="11.125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="11.33203125" style="1" customWidth="1"/>
+    <col min="37" max="42" width="7.21875" style="1" customWidth="1"/>
+    <col min="43" max="43" width="11.109375" style="1" customWidth="1"/>
     <col min="44" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="21" customHeight="1">
+    <row r="1" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="50" t="s">
         <v>68</v>
       </c>
@@ -8898,7 +8834,7 @@
       <c r="AG1" s="72"/>
       <c r="AH1" s="72"/>
     </row>
-    <row r="2" spans="1:43" ht="21" customHeight="1">
+    <row r="2" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="63" t="s">
         <v>67</v>
       </c>
@@ -9001,7 +8937,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:43" ht="21" customHeight="1">
+    <row r="3" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
         <v>1.5</v>
       </c>
@@ -9107,7 +9043,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="21" customHeight="1">
+    <row r="4" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
         <v>2.5</v>
       </c>
@@ -9197,7 +9133,7 @@
       <c r="AP4" s="83"/>
       <c r="AQ4" s="84"/>
     </row>
-    <row r="5" spans="1:43" ht="21" customHeight="1">
+    <row r="5" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -9303,7 +9239,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="21" customHeight="1">
+    <row r="6" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -9409,7 +9345,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="21" customHeight="1">
+    <row r="7" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
         <v>10</v>
       </c>
@@ -9515,7 +9451,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="21" customHeight="1">
+    <row r="8" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2">
         <v>16</v>
       </c>
@@ -9597,7 +9533,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="21" customHeight="1">
+    <row r="9" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2">
         <v>25</v>
       </c>
@@ -9680,7 +9616,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="21" customHeight="1">
+    <row r="10" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2">
         <v>35</v>
       </c>
@@ -9763,7 +9699,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="21" customHeight="1">
+    <row r="11" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2">
         <v>50</v>
       </c>
@@ -9846,7 +9782,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="21" customHeight="1">
+    <row r="12" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2">
         <v>70</v>
       </c>
@@ -9929,7 +9865,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="21" customHeight="1">
+    <row r="13" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2">
         <v>95</v>
       </c>
@@ -10008,7 +9944,7 @@
       </c>
       <c r="AH13" s="77"/>
     </row>
-    <row r="14" spans="1:43" ht="21" customHeight="1">
+    <row r="14" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2">
         <v>120</v>
       </c>
@@ -10081,7 +10017,7 @@
       </c>
       <c r="AH14" s="77"/>
     </row>
-    <row r="15" spans="1:43" ht="21" customHeight="1">
+    <row r="15" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2">
         <v>150</v>
       </c>
@@ -10154,7 +10090,7 @@
       </c>
       <c r="AH15" s="77"/>
     </row>
-    <row r="16" spans="1:43" ht="21" customHeight="1">
+    <row r="16" spans="1:43" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2">
         <v>185</v>
       </c>
@@ -10227,7 +10163,7 @@
       </c>
       <c r="AH16" s="77"/>
     </row>
-    <row r="17" spans="1:34" ht="21" customHeight="1">
+    <row r="17" spans="1:34" ht="20.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2">
         <v>240</v>
       </c>
@@ -10300,7 +10236,7 @@
       </c>
       <c r="AH17" s="77"/>
     </row>
-    <row r="18" spans="1:34" ht="21" customHeight="1">
+    <row r="18" spans="1:34" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>300</v>
       </c>
@@ -10359,7 +10295,7 @@
       <c r="V18" s="90"/>
       <c r="W18" s="90"/>
     </row>
-    <row r="19" spans="1:34" ht="21" customHeight="1">
+    <row r="19" spans="1:34" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>400</v>
       </c>
@@ -10390,7 +10326,7 @@
       <c r="V19" s="91"/>
       <c r="W19" s="91"/>
     </row>
-    <row r="20" spans="1:34" ht="21" customHeight="1">
+    <row r="20" spans="1:34" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>500</v>
       </c>
@@ -10421,7 +10357,7 @@
       <c r="V20" s="91"/>
       <c r="W20" s="91"/>
     </row>
-    <row r="21" spans="1:34" ht="21" customHeight="1">
+    <row r="21" spans="1:34" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>630</v>
       </c>
@@ -10452,10 +10388,18 @@
       <c r="V21" s="91"/>
       <c r="W21" s="91"/>
     </row>
-    <row r="22" spans="1:34" ht="21" customHeight="1">
+    <row r="22" spans="1:34" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68"/>
     </row>
-    <row r="27" spans="1:34" ht="21" customHeight="1">
+    <row r="23" spans="1:34" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="101">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="49"/>
       <c r="D27" s="49"/>
       <c r="E27" s="49"/>
@@ -10467,7 +10411,7 @@
       <c r="L27" s="49"/>
       <c r="M27" s="49"/>
     </row>
-    <row r="53" spans="3:23" ht="21" customHeight="1">
+    <row r="53" spans="3:23" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="49"/>
       <c r="D53" s="49"/>
       <c r="E53" s="49"/>
@@ -10490,7 +10434,7 @@
       <c r="V53" s="49"/>
       <c r="W53" s="49"/>
     </row>
-    <row r="78" spans="3:23" ht="21" customHeight="1">
+    <row r="78" spans="3:23" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="49"/>
       <c r="D78" s="49"/>
       <c r="E78" s="49"/>
@@ -10513,77 +10457,77 @@
       <c r="V78" s="49"/>
       <c r="W78" s="49"/>
     </row>
-    <row r="110" spans="20:20" s="15" customFormat="1" ht="21" customHeight="1">
+    <row r="110" spans="20:20" s="15" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T110" s="97"/>
     </row>
-    <row r="111" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="111" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T111" s="98"/>
     </row>
-    <row r="112" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="112" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T112" s="98"/>
     </row>
-    <row r="113" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="113" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T113" s="98"/>
     </row>
-    <row r="114" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="114" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T114" s="98"/>
     </row>
-    <row r="115" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="115" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T115" s="98"/>
     </row>
-    <row r="116" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="116" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T116" s="98"/>
     </row>
-    <row r="117" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="117" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T117" s="98"/>
     </row>
-    <row r="118" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="118" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T118" s="98"/>
     </row>
-    <row r="119" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="119" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T119" s="98"/>
     </row>
-    <row r="120" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="120" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T120" s="98"/>
     </row>
-    <row r="121" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="121" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T121" s="98"/>
     </row>
-    <row r="122" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="122" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T122" s="98"/>
     </row>
-    <row r="123" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="123" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T123" s="98"/>
     </row>
-    <row r="124" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="124" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T124" s="98"/>
     </row>
-    <row r="125" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="125" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T125" s="98"/>
     </row>
-    <row r="126" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="126" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T126" s="98"/>
     </row>
-    <row r="127" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="127" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T127" s="98"/>
     </row>
-    <row r="128" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="128" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T128" s="98"/>
     </row>
-    <row r="129" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="129" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T129" s="98"/>
     </row>
-    <row r="130" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="130" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T130" s="98"/>
     </row>
-    <row r="131" spans="20:20" s="60" customFormat="1" ht="21" customHeight="1">
+    <row r="131" spans="20:20" s="60" customFormat="1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T131" s="98"/>
     </row>
-    <row r="281" spans="1:2" ht="21" customHeight="1">
+    <row r="281" spans="1:2" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="7"/>
     </row>
-    <row r="376" spans="1:1" ht="21" customHeight="1">
+    <row r="376" spans="1:1" ht="20.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="5"/>
     </row>
   </sheetData>
@@ -10595,25 +10539,25 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987FCB26-D6AC-4188-8105-3C3B4522385C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.8" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="66" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" style="66" customWidth="1"/>
     <col min="2" max="2" width="12" style="66" customWidth="1"/>
-    <col min="3" max="4" width="10.875" style="67" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.88671875" style="67" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" style="67" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="67"/>
-    <col min="7" max="7" width="4.125" style="67" customWidth="1"/>
-    <col min="8" max="8" width="11.625" style="67" customWidth="1"/>
-    <col min="9" max="9" width="12.75" style="67" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" style="67" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="67" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="67" customWidth="1"/>
     <col min="10" max="16384" width="9" style="67"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="80" t="s">
         <v>74</v>
       </c>
@@ -10629,17 +10573,11 @@
       <c r="E1" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="102" t="s">
-        <v>496</v>
-      </c>
-      <c r="H1" s="103">
-        <v>46190</v>
-      </c>
-      <c r="I1" s="102" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="G1" s="102"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="102"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="80" t="s">
         <v>493</v>
       </c>
@@ -10657,7 +10595,7 @@
         <v>13.940265745090068</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="80" t="s">
         <v>493</v>
       </c>
@@ -10675,7 +10613,7 @@
         <v>8.5546914479563618</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="80" t="s">
         <v>493</v>
       </c>
@@ -10693,7 +10631,7 @@
         <v>5.3385094517275791</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="80" t="s">
         <v>493</v>
       </c>
@@ -10711,7 +10649,7 @@
         <v>3.5811992352875026</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="80" t="s">
         <v>493</v>
       </c>
@@ -10729,7 +10667,7 @@
         <v>2.1385838959213781</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="80" t="s">
         <v>493</v>
       </c>
@@ -10747,7 +10685,7 @@
         <v>1.3597198152277512</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="80" t="s">
         <v>493</v>
       </c>
@@ -10765,7 +10703,7 @@
         <v>0.87479417118549285</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="80" t="s">
         <v>493</v>
       </c>
@@ -10783,7 +10721,7 @@
         <v>0.64047367948130152</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="80" t="s">
         <v>493</v>
       </c>
@@ -10801,7 +10739,7 @@
         <v>0.49382733785071775</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="80" t="s">
         <v>493</v>
       </c>
@@ -10819,7 +10757,7 @@
         <v>0.35491969757967468</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="80" t="s">
         <v>493</v>
       </c>
@@ -10837,7 +10775,7 @@
         <v>0.26920175263249763</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" s="80" t="s">
         <v>493</v>
       </c>
@@ -10855,7 +10793,7 @@
         <v>0.22181972699169381</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" s="80" t="s">
         <v>493</v>
       </c>
@@ -10873,7 +10811,7 @@
         <v>0.18894024810790436</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" s="80" t="s">
         <v>493</v>
       </c>
@@ -10891,7 +10829,7 @@
         <v>0.16010794720298566</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="80" t="s">
         <v>493</v>
       </c>
@@ -10909,7 +10847,7 @@
         <v>0.13277334539314836</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="80" t="s">
         <v>493</v>
       </c>
@@ -10927,7 +10865,7 @@
         <v>0.11550181145653593</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="80" t="s">
         <v>494</v>
       </c>
@@ -10945,7 +10883,7 @@
         <v>13.940265745090068</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="80" t="s">
         <v>494</v>
       </c>
@@ -10963,7 +10901,7 @@
         <v>8.5546914479563618</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="80" t="s">
         <v>494</v>
       </c>
@@ -10981,7 +10919,7 @@
         <v>5.3385094517275791</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="80" t="s">
         <v>494</v>
       </c>
@@ -10999,7 +10937,7 @@
         <v>3.5811992352875026</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="80" t="s">
         <v>494</v>
       </c>
@@ -11017,7 +10955,7 @@
         <v>2.1385838959213781</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="80" t="s">
         <v>494</v>
       </c>
@@ -11035,7 +10973,7 @@
         <v>1.3606198152277513</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="80" t="s">
         <v>494</v>
       </c>
@@ -11053,7 +10991,7 @@
         <v>0.87479417118549285</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="80" t="s">
         <v>494</v>
       </c>
@@ -11071,7 +11009,7 @@
         <v>0.64137367948130153</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="80" t="s">
         <v>494</v>
       </c>
@@ -11089,7 +11027,7 @@
         <v>0.48348137857638279</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="80" t="s">
         <v>494</v>
       </c>
@@ -11107,7 +11045,7 @@
         <v>0.34697113272428715</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="80" t="s">
         <v>494</v>
       </c>
@@ -11125,7 +11063,7 @@
         <v>0.26051217495670814</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="80" t="s">
         <v>494</v>
       </c>
@@ -11143,7 +11081,7 @@
         <v>0.21443781899896655</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="80" t="s">
         <v>494</v>
       </c>
@@ -11161,7 +11099,7 @@
         <v>0.18135576394614358</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="80" t="s">
         <v>494</v>
       </c>
@@ -11179,7 +11117,7 @@
         <v>0.15376370889332058</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="80" t="s">
         <v>494</v>
       </c>
@@ -11197,7 +11135,7 @@
         <v>0.12691423000953111</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="80" t="s">
         <v>494</v>
       </c>
@@ -11215,7 +11153,7 @@
         <v>0.10995910708348328</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="80" t="s">
         <v>495</v>
       </c>
@@ -11233,7 +11171,7 @@
         <v>13.940265745090068</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="80" t="s">
         <v>495</v>
       </c>
@@ -11251,7 +11189,7 @@
         <v>8.5546914479563618</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="80" t="s">
         <v>495</v>
       </c>
@@ -11269,7 +11207,7 @@
         <v>5.3385094517275791</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="80" t="s">
         <v>495</v>
       </c>
@@ -11287,7 +11225,7 @@
         <v>3.5811992352875026</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="80" t="s">
         <v>495</v>
       </c>
@@ -11305,7 +11243,7 @@
         <v>2.1385838959213781</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="80" t="s">
         <v>495</v>
       </c>
@@ -11323,7 +11261,7 @@
         <v>1.3606198152277513</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="80" t="s">
         <v>495</v>
       </c>
@@ -11341,7 +11279,7 @@
         <v>0.87479417118549285</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="80" t="s">
         <v>495</v>
       </c>
@@ -11359,7 +11297,7 @@
         <v>0.64137367948130153</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="80" t="s">
         <v>495</v>
       </c>
@@ -11377,7 +11315,7 @@
         <v>0.48348137857638279</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="80" t="s">
         <v>495</v>
       </c>
@@ -11395,7 +11333,7 @@
         <v>0.34697113272428715</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="80" t="s">
         <v>495</v>
       </c>
@@ -11413,7 +11351,7 @@
         <v>0.26051217495670814</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="80" t="s">
         <v>495</v>
       </c>
@@ -11431,7 +11369,7 @@
         <v>0.21533781899896656</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="80" t="s">
         <v>495</v>
       </c>
@@ -11449,7 +11387,7 @@
         <v>0.18225576394614357</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A47" s="80" t="s">
         <v>495</v>
       </c>
@@ -11467,7 +11405,7 @@
         <v>0.1546637088933206</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="80" t="s">
         <v>495</v>
       </c>
@@ -11485,7 +11423,7 @@
         <v>0.12808423000953112</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" s="80" t="s">
         <v>495</v>
       </c>
@@ -11501,6 +11439,17 @@
       <c r="E49" s="79">
         <f t="shared" si="0"/>
         <v>0.11121910708348327</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A51" s="102" t="s">
+        <v>496</v>
+      </c>
+      <c r="B51" s="103">
+        <v>46190</v>
+      </c>
+      <c r="C51" s="102" t="s">
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -11511,43 +11460,44 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CBD7EA6-58F4-4FDE-95F2-DFB83D2013C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A2:G48"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.8" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8.375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="6.25" style="4" customWidth="1"/>
-    <col min="3" max="7" width="5.375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="6.21875" style="4" customWidth="1"/>
+    <col min="3" max="7" width="5.33203125" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7">
-      <c r="A2" s="75" t="s">
+    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A2" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="111" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="75">
+      <c r="C2" s="111">
         <v>4</v>
       </c>
-      <c r="D2" s="75">
+      <c r="D2" s="111">
         <v>6</v>
       </c>
-      <c r="E2" s="75">
+      <c r="E2" s="111">
         <v>10</v>
       </c>
-      <c r="F2" s="75">
+      <c r="F2" s="111">
         <v>15</v>
       </c>
-      <c r="G2" s="75">
+      <c r="G2" s="111">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="74" t="s">
         <v>83</v>
       </c>
@@ -11570,7 +11520,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="74" t="s">
         <v>83</v>
       </c>
@@ -11593,7 +11543,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="74" t="s">
         <v>83</v>
       </c>
@@ -11616,7 +11566,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="74" t="s">
         <v>83</v>
       </c>
@@ -11639,7 +11589,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="74" t="s">
         <v>83</v>
       </c>
@@ -11662,7 +11612,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="74" t="s">
         <v>83</v>
       </c>
@@ -11685,7 +11635,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="74" t="s">
         <v>83</v>
       </c>
@@ -11708,7 +11658,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" s="74" t="s">
         <v>83</v>
       </c>
@@ -11731,7 +11681,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="74" t="s">
         <v>83</v>
       </c>
@@ -11754,7 +11704,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" s="74" t="s">
         <v>83</v>
       </c>
@@ -11777,7 +11727,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A13" s="74" t="s">
         <v>83</v>
       </c>
@@ -11800,7 +11750,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A14" s="74" t="s">
         <v>83</v>
       </c>
@@ -11823,7 +11773,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" s="74" t="s">
         <v>83</v>
       </c>
@@ -11846,7 +11796,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" s="74" t="s">
         <v>83</v>
       </c>
@@ -11869,7 +11819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="74" t="s">
         <v>83</v>
       </c>
@@ -11892,7 +11842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="74" t="s">
         <v>83</v>
       </c>
@@ -11915,7 +11865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="74" t="s">
         <v>83</v>
       </c>
@@ -11938,7 +11888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="74" t="s">
         <v>83</v>
       </c>
@@ -11961,7 +11911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="74" t="s">
         <v>84</v>
       </c>
@@ -11984,7 +11934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="74" t="s">
         <v>84</v>
       </c>
@@ -12007,7 +11957,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="74" t="s">
         <v>84</v>
       </c>
@@ -12030,7 +11980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="74" t="s">
         <v>84</v>
       </c>
@@ -12053,7 +12003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="74" t="s">
         <v>84</v>
       </c>
@@ -12076,7 +12026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="74" t="s">
         <v>84</v>
       </c>
@@ -12099,7 +12049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="74" t="s">
         <v>84</v>
       </c>
@@ -12122,7 +12072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="74" t="s">
         <v>84</v>
       </c>
@@ -12145,7 +12095,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="74" t="s">
         <v>84</v>
       </c>
@@ -12168,7 +12118,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="74" t="s">
         <v>84</v>
       </c>
@@ -12191,7 +12141,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="74" t="s">
         <v>85</v>
       </c>
@@ -12214,7 +12164,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="74" t="s">
         <v>85</v>
       </c>
@@ -12237,7 +12187,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="74" t="s">
         <v>85</v>
       </c>
@@ -12260,7 +12210,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="74" t="s">
         <v>85</v>
       </c>
@@ -12283,7 +12233,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="74" t="s">
         <v>85</v>
       </c>
@@ -12306,7 +12256,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="74" t="s">
         <v>85</v>
       </c>
@@ -12329,7 +12279,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="74" t="s">
         <v>85</v>
       </c>
@@ -12352,7 +12302,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="74" t="s">
         <v>85</v>
       </c>
@@ -12375,7 +12325,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="74" t="s">
         <v>85</v>
       </c>
@@ -12398,7 +12348,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="74" t="s">
         <v>85</v>
       </c>
@@ -12421,7 +12371,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="74" t="s">
         <v>85</v>
       </c>
@@ -12444,7 +12394,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="74" t="s">
         <v>85</v>
       </c>
@@ -12467,7 +12417,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="74" t="s">
         <v>85</v>
       </c>
@@ -12490,7 +12440,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="74" t="s">
         <v>85</v>
       </c>
@@ -12513,7 +12463,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="74" t="s">
         <v>85</v>
       </c>
@@ -12536,7 +12486,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="74" t="s">
         <v>85</v>
       </c>
@@ -12559,7 +12509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="74" t="s">
         <v>85</v>
       </c>
@@ -12582,7 +12532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="74" t="s">
         <v>85</v>
       </c>
@@ -12608,22 +12558,21 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C03EFB2-E90C-46B8-BF3E-7F0DA16A71A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.8" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="85" t="s">
         <v>96</v>
       </c>
@@ -12637,7 +12586,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="74" t="s">
         <v>95</v>
       </c>
@@ -12651,7 +12600,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="74" t="s">
         <v>95</v>
       </c>
@@ -12665,7 +12614,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="74" t="s">
         <v>95</v>
       </c>
@@ -12679,7 +12628,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="74" t="s">
         <v>95</v>
       </c>
@@ -12693,7 +12642,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="74" t="s">
         <v>95</v>
       </c>
@@ -12707,7 +12656,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="74" t="s">
         <v>95</v>
       </c>
@@ -12721,7 +12670,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="74" t="s">
         <v>95</v>
       </c>
@@ -12735,7 +12684,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="74" t="s">
         <v>95</v>
       </c>
@@ -12749,7 +12698,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="74" t="s">
         <v>95</v>
       </c>
@@ -12763,7 +12712,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="74" t="s">
         <v>95</v>
       </c>
@@ -12777,7 +12726,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" s="74" t="s">
         <v>95</v>
       </c>
@@ -12791,7 +12740,7 @@
         <v>0.79500000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" s="74" t="s">
         <v>95</v>
       </c>
@@ -12805,7 +12754,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="74" t="s">
         <v>95</v>
       </c>
@@ -12819,7 +12768,7 @@
         <v>0.80500000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="74" t="s">
         <v>95</v>
       </c>
@@ -12833,7 +12782,7 @@
         <v>0.81499999999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" s="74" t="s">
         <v>95</v>
       </c>
@@ -12847,7 +12796,7 @@
         <v>0.81499999999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="74" t="s">
         <v>95</v>
       </c>
@@ -12861,7 +12810,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="74" t="s">
         <v>95</v>
       </c>
@@ -12875,7 +12824,7 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="74" t="s">
         <v>95</v>
       </c>
@@ -12889,7 +12838,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="74" t="s">
         <v>95</v>
       </c>
@@ -12903,7 +12852,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="74" t="s">
         <v>95</v>
       </c>
@@ -12917,7 +12866,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="74" t="s">
         <v>95</v>
       </c>
@@ -12931,7 +12880,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="74" t="s">
         <v>95</v>
       </c>
@@ -12945,7 +12894,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="74" t="s">
         <v>95</v>
       </c>
@@ -12967,163 +12916,163 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE904A19-6CAC-4EC0-9703-DF18CFDF1B84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A2:C31"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="82"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="87">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="87">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="87">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="87">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="87">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="87">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="87">
         <v>75</v>
       </c>
       <c r="C9" s="81"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="87">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="87">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="87">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="87">
         <v>175</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="87">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="87">
         <v>225</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="87">
         <v>250</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="87">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="87">
         <v>350</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="87">
         <v>400</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="87">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="87">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="87">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="87">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="87">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="87">
         <v>1000</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="87">
         <v>1250</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="87">
         <v>1600</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="87">
         <v>2000</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="87">
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="87">
         <v>5000</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="87">
         <v>6300</v>
       </c>
@@ -13135,28 +13084,28 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C36C23-C8D5-43FA-9B8C-2C213D4932B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet18">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:AG83"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="17.100000000000001" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="17.2" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="46" customWidth="1"/>
-    <col min="2" max="2" width="6.25" style="47" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="47" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="48" customWidth="1"/>
-    <col min="5" max="5" width="7.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.75" style="1" customWidth="1"/>
-    <col min="7" max="8" width="6.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.5" style="1" customWidth="1"/>
-    <col min="12" max="33" width="9.375" style="1" customWidth="1"/>
-    <col min="34" max="16384" width="11.125" style="1"/>
+    <col min="1" max="1" width="9.44140625" style="46" customWidth="1"/>
+    <col min="2" max="2" width="6.21875" style="47" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" style="47" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" style="48" customWidth="1"/>
+    <col min="5" max="5" width="7.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.77734375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="6.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.77734375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.44140625" style="1" customWidth="1"/>
+    <col min="12" max="33" width="9.33203125" style="1" customWidth="1"/>
+    <col min="34" max="16384" width="11.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="1" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -13257,13 +13206,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="2" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="3" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="109" t="s">
         <v>51</v>
       </c>
@@ -13326,7 +13275,7 @@
       <c r="AF3" s="14"/>
       <c r="AG3" s="14"/>
     </row>
-    <row r="4" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="4" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="110"/>
       <c r="B4" s="108"/>
       <c r="C4" s="108"/>
@@ -13409,7 +13358,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="5" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>1E-3</v>
       </c>
@@ -13484,7 +13433,7 @@
       <c r="AF5" s="25"/>
       <c r="AG5" s="26"/>
     </row>
-    <row r="6" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="6" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="27">
         <v>0.2</v>
       </c>
@@ -13567,7 +13516,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="7" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="27">
         <v>0.25</v>
       </c>
@@ -13651,7 +13600,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="8" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27">
         <v>0.4</v>
       </c>
@@ -13734,7 +13683,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="9" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="27">
         <v>0.5</v>
       </c>
@@ -13818,7 +13767,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="15.75" customHeight="1">
+    <row r="10" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27">
         <v>0.74</v>
       </c>
@@ -13902,7 +13851,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="11" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="27">
         <v>0.75</v>
       </c>
@@ -13985,7 +13934,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="15.75" customHeight="1">
+    <row r="12" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="27">
         <v>0.79</v>
       </c>
@@ -14069,7 +14018,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="15.75" customHeight="1">
+    <row r="13" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="27">
         <v>0.9</v>
       </c>
@@ -14153,7 +14102,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="15.75" customHeight="1">
+    <row r="14" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27">
         <v>1.1000000000000001</v>
       </c>
@@ -14237,7 +14186,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="15.75" customHeight="1">
+    <row r="15" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="27">
         <v>1.1499999999999999</v>
       </c>
@@ -14321,7 +14270,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="15.75" customHeight="1">
+    <row r="16" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="27">
         <v>1.3</v>
       </c>
@@ -14405,7 +14354,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="17" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="27">
         <v>1.5</v>
       </c>
@@ -14488,7 +14437,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="18" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27">
         <v>1.55</v>
       </c>
@@ -14572,7 +14521,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="19" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27">
         <v>1.6</v>
       </c>
@@ -14656,7 +14605,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="20" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="27">
         <v>1.8</v>
       </c>
@@ -14740,7 +14689,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="21" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="27">
         <v>1.9</v>
       </c>
@@ -14824,7 +14773,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="22" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="27">
         <v>1.95</v>
       </c>
@@ -14908,7 +14857,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="23" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27">
         <v>2.2000000000000002</v>
       </c>
@@ -14987,7 +14936,7 @@
       <c r="AF23" s="25"/>
       <c r="AG23" s="26"/>
     </row>
-    <row r="24" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="24" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="27">
         <v>2.25</v>
       </c>
@@ -15071,7 +15020,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="25" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="27">
         <v>2.2999999999999998</v>
       </c>
@@ -15155,7 +15104,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="26" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="27">
         <v>2.5</v>
       </c>
@@ -15239,7 +15188,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="27" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="27">
         <v>2.6</v>
       </c>
@@ -15323,7 +15272,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="28" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="27">
         <v>2.65</v>
       </c>
@@ -15407,7 +15356,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="29" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="27">
         <v>2.7</v>
       </c>
@@ -15491,7 +15440,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="30" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="27">
         <v>2.8</v>
       </c>
@@ -15575,7 +15524,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="31" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="27">
         <v>2.9</v>
       </c>
@@ -15659,7 +15608,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="32" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27">
         <v>2.95</v>
       </c>
@@ -15743,7 +15692,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="33" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="27">
         <v>3</v>
       </c>
@@ -15827,7 +15776,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="34" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="27">
         <v>3.25</v>
       </c>
@@ -15911,7 +15860,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="35" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="27">
         <v>3.3</v>
       </c>
@@ -15995,7 +15944,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="36" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="27">
         <v>3.44</v>
       </c>
@@ -16079,7 +16028,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="37" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="27">
         <v>3.5</v>
       </c>
@@ -16163,7 +16112,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="38" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="27">
         <v>3.7</v>
       </c>
@@ -16248,7 +16197,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="39" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="27">
         <v>3.75</v>
       </c>
@@ -16334,7 +16283,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="40" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="27">
         <v>4.2</v>
       </c>
@@ -16420,7 +16369,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="41" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="27">
         <v>4.4000000000000004</v>
       </c>
@@ -16506,7 +16455,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="42" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="27">
         <v>4.45</v>
       </c>
@@ -16592,7 +16541,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="43" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="27">
         <v>4.5</v>
       </c>
@@ -16678,7 +16627,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="44" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="27">
         <v>4.7</v>
       </c>
@@ -16764,7 +16713,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="45" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="27">
         <v>5.2</v>
       </c>
@@ -16850,7 +16799,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="46" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="27">
         <v>5.5</v>
       </c>
@@ -16939,7 +16888,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="47" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="27">
         <v>5.95</v>
       </c>
@@ -17029,7 +16978,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="48" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="27">
         <v>6</v>
       </c>
@@ -17119,7 +17068,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="49" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="27">
         <v>6.25</v>
       </c>
@@ -17209,7 +17158,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="50" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="27">
         <v>7</v>
       </c>
@@ -17299,7 +17248,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="51" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="27">
         <v>7.4</v>
       </c>
@@ -17389,7 +17338,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="52" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="27">
         <v>7.5</v>
       </c>
@@ -17482,7 +17431,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="53" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="27">
         <v>7.75</v>
       </c>
@@ -17576,7 +17525,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="54" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="27">
         <v>8.4</v>
       </c>
@@ -17670,7 +17619,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="55" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="27">
         <v>8.85</v>
       </c>
@@ -17764,7 +17713,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="56" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="27">
         <v>11</v>
       </c>
@@ -17857,7 +17806,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="57" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="27">
         <v>11.1</v>
       </c>
@@ -17951,7 +17900,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="58" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="27">
         <v>11.25</v>
       </c>
@@ -18045,7 +17994,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="59" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="27">
         <v>11.75</v>
       </c>
@@ -18139,7 +18088,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="60" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="27">
         <v>12</v>
       </c>
@@ -18233,7 +18182,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="61" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="27">
         <v>13.6</v>
       </c>
@@ -18327,7 +18276,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="62" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="27">
         <v>14.35</v>
       </c>
@@ -18421,7 +18370,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="63" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="27">
         <v>15</v>
       </c>
@@ -18514,7 +18463,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="64" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="27">
         <v>15.4</v>
       </c>
@@ -18608,7 +18557,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="65" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="27">
         <v>16.5</v>
       </c>
@@ -18702,7 +18651,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="66" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="27">
         <v>18.5</v>
       </c>
@@ -18795,7 +18744,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="67" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="27">
         <v>22</v>
       </c>
@@ -18888,7 +18837,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="68" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="27">
         <v>22.35</v>
       </c>
@@ -18982,7 +18931,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="69" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="27">
         <v>22.9</v>
       </c>
@@ -19076,7 +19025,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="70" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="27">
         <v>28.45</v>
       </c>
@@ -19170,7 +19119,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="17.25" customHeight="1">
+    <row r="71" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="27">
         <v>30</v>
       </c>
@@ -19265,7 +19214,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="72" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="27">
         <v>37</v>
       </c>
@@ -19360,7 +19309,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="73" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="27">
         <v>45</v>
       </c>
@@ -19455,7 +19404,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="74" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="27">
         <v>55</v>
       </c>
@@ -19556,7 +19505,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="75" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="27">
         <v>75</v>
       </c>
@@ -19657,7 +19606,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="16.5" customHeight="1">
+    <row r="76" spans="1:33" ht="16.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="27">
         <v>90</v>
       </c>
@@ -19754,7 +19703,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="77" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="27">
         <v>110</v>
       </c>
@@ -19851,7 +19800,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="78" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="27">
         <v>132</v>
       </c>
@@ -19938,7 +19887,7 @@
       </c>
       <c r="AG78" s="26"/>
     </row>
-    <row r="79" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="79" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="27">
         <v>150</v>
       </c>
@@ -20017,7 +19966,7 @@
       </c>
       <c r="AG79" s="26"/>
     </row>
-    <row r="80" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="80" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="32">
         <v>262</v>
       </c>
@@ -20080,7 +20029,7 @@
       </c>
       <c r="AG80" s="42"/>
     </row>
-    <row r="81" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="81" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="43"/>
       <c r="B81" s="44"/>
       <c r="C81" s="44"/>
@@ -20115,7 +20064,7 @@
       <c r="AF81" s="3"/>
       <c r="AG81" s="3"/>
     </row>
-    <row r="82" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="82" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="43"/>
       <c r="B82" s="44"/>
       <c r="C82" s="44"/>
@@ -20150,7 +20099,7 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
     </row>
-    <row r="83" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="83" spans="1:33" ht="17.2" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="43"/>
       <c r="B83" s="44"/>
       <c r="C83" s="44"/>
